--- a/test_data/PQME_Encounter_Test_Data.xlsx
+++ b/test_data/PQME_Encounter_Test_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rishi Files\OrthoLegal_Automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8B24D4-D027-4F90-84AA-091245D9C6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B521AA1F-2FC3-4214-9365-E7382A67FD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="1092" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="118">
   <si>
     <t>Applicant Details</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Upload Documents</t>
+  </si>
+  <si>
+    <t>Interpreter Details</t>
   </si>
   <si>
     <t>Applicant Attorney Details</t>
@@ -139,6 +142,15 @@
     <t>Upload Attorney Demos</t>
   </si>
   <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Vendor Phone</t>
+  </si>
+  <si>
     <t>Firm</t>
   </si>
   <si>
@@ -193,10 +205,10 @@
     <t>A</t>
   </si>
   <si>
-    <t>446-21-9974</t>
+    <t>Male</t>
   </si>
   <si>
-    <t>Male</t>
+    <t>446-21-9974</t>
   </si>
   <si>
     <t>1234 Main St</t>
@@ -229,6 +241,9 @@
     <t>01/15/2024</t>
   </si>
   <si>
+    <t>Neck</t>
+  </si>
+  <si>
     <t>WCAB-123456789</t>
   </si>
   <si>
@@ -245,6 +260,9 @@
   </si>
   <si>
     <t>Applicant Attorney</t>
+  </si>
+  <si>
+    <t>Golden Valley Family Clinic - 2450 Harbor Boulevard, Suite 210, Building B</t>
   </si>
   <si>
     <t>Costa Mesa</t>
@@ -349,17 +367,20 @@
     <t>assistant1@dummy.com</t>
   </si>
   <si>
-    <t>Golden Valley Family Clinic - 2450 Harbor Boulevard, Suite 210, Building B</t>
+    <t>Chinese - Mandarin</t>
   </si>
   <si>
-    <t>Neck</t>
+    <t>Interpreto ChineseMandarin</t>
+  </si>
+  <si>
+    <t>(714) 555-2389</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,13 +414,39 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -424,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -434,10 +481,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -743,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CF202"/>
+  <dimension ref="A1:CI202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -777,480 +831,498 @@
     <col min="32" max="32" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="16" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="5.5703125" customWidth="1"/>
+    <col min="46" max="46" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="55" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.5703125" customWidth="1"/>
+    <col min="56" max="56" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="27" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="24" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="5.5703125" customWidth="1"/>
+    <col min="68" max="68" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="70" max="70" width="23" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="23" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="27" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="24" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="23" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="13.7109375" customWidth="1"/>
+    <col min="86" max="86" width="22.85546875" customWidth="1"/>
+    <col min="87" max="87" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:87" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="7" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="7" t="s">
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="7" t="s">
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="10"/>
+      <c r="AD1" s="10"/>
+      <c r="AE1" s="10"/>
+      <c r="AF1" s="10"/>
+      <c r="AG1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="9" t="s">
+      <c r="AH1" s="10"/>
+      <c r="AI1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="8"/>
-      <c r="AL1" s="8"/>
-      <c r="AM1" s="8"/>
-      <c r="AN1" s="8"/>
-      <c r="AO1" s="8"/>
-      <c r="AP1" s="8"/>
-      <c r="AQ1" s="8"/>
-      <c r="AR1" s="8"/>
-      <c r="AS1" s="8"/>
-      <c r="AT1" s="8"/>
-      <c r="AU1" s="8"/>
-      <c r="AV1" s="7" t="s">
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AW1" s="8"/>
-      <c r="AX1" s="8"/>
-      <c r="AY1" s="8"/>
-      <c r="AZ1" s="8"/>
-      <c r="BA1" s="8"/>
-      <c r="BB1" s="8"/>
-      <c r="BC1" s="8"/>
-      <c r="BD1" s="8"/>
-      <c r="BE1" s="7" t="s">
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="10"/>
+      <c r="AO1" s="10"/>
+      <c r="AP1" s="10"/>
+      <c r="AQ1" s="10"/>
+      <c r="AR1" s="10"/>
+      <c r="AS1" s="10"/>
+      <c r="AT1" s="10"/>
+      <c r="AU1" s="10"/>
+      <c r="AV1" s="10"/>
+      <c r="AW1" s="10"/>
+      <c r="AX1" s="10"/>
+      <c r="AY1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="BF1" s="8"/>
-      <c r="BG1" s="8"/>
-      <c r="BH1" s="8"/>
-      <c r="BI1" s="8"/>
-      <c r="BJ1" s="8"/>
-      <c r="BK1" s="8"/>
-      <c r="BL1" s="8"/>
-      <c r="BM1" s="8"/>
-      <c r="BN1" s="8"/>
-      <c r="BO1" s="8"/>
-      <c r="BP1" s="8"/>
-      <c r="BQ1" s="8"/>
-      <c r="BR1" s="7" t="s">
+      <c r="AZ1" s="10"/>
+      <c r="BA1" s="10"/>
+      <c r="BB1" s="10"/>
+      <c r="BC1" s="10"/>
+      <c r="BD1" s="10"/>
+      <c r="BE1" s="10"/>
+      <c r="BF1" s="10"/>
+      <c r="BG1" s="10"/>
+      <c r="BH1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="BS1" s="8"/>
-      <c r="BT1" s="8"/>
-      <c r="BU1" s="8"/>
-      <c r="BV1" s="8"/>
-      <c r="BW1" s="8"/>
-      <c r="BX1" s="8"/>
-      <c r="BY1" s="8"/>
-      <c r="BZ1" s="8"/>
-      <c r="CA1" s="8"/>
-      <c r="CB1" s="8"/>
-      <c r="CC1" s="8"/>
-      <c r="CD1" s="8"/>
-      <c r="CE1" s="8"/>
-      <c r="CF1" s="8"/>
-    </row>
-    <row r="2" spans="1:84" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="BI1" s="10"/>
+      <c r="BJ1" s="10"/>
+      <c r="BK1" s="10"/>
+      <c r="BL1" s="10"/>
+      <c r="BM1" s="10"/>
+      <c r="BN1" s="10"/>
+      <c r="BO1" s="10"/>
+      <c r="BP1" s="10"/>
+      <c r="BQ1" s="10"/>
+      <c r="BR1" s="10"/>
+      <c r="BS1" s="10"/>
+      <c r="BT1" s="10"/>
+      <c r="BU1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="BV1" s="10"/>
+      <c r="BW1" s="10"/>
+      <c r="BX1" s="10"/>
+      <c r="BY1" s="10"/>
+      <c r="BZ1" s="10"/>
+      <c r="CA1" s="10"/>
+      <c r="CB1" s="10"/>
+      <c r="CC1" s="10"/>
+      <c r="CD1" s="10"/>
+      <c r="CE1" s="10"/>
+      <c r="CF1" s="10"/>
+      <c r="CG1" s="10"/>
+      <c r="CH1" s="10"/>
+      <c r="CI1" s="10"/>
+    </row>
+    <row r="2" spans="1:87" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="AB2" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="AC2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AF2" s="1" t="s">
-        <v>36</v>
+      <c r="AT2" s="1" t="s">
+        <v>19</v>
       </c>
-      <c r="AG2" s="1" t="s">
-        <v>37</v>
+      <c r="AU2" s="1" t="s">
+        <v>44</v>
       </c>
-      <c r="AH2" s="1" t="s">
-        <v>38</v>
+      <c r="AV2" s="1" t="s">
+        <v>45</v>
       </c>
-      <c r="AI2" s="1" t="s">
-        <v>39</v>
+      <c r="AW2" s="1" t="s">
+        <v>23</v>
       </c>
-      <c r="AJ2" s="1" t="s">
-        <v>8</v>
+      <c r="AX2" s="1" t="s">
+        <v>46</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BI2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AM2" s="1" t="s">
-        <v>14</v>
+      <c r="BK2" s="1" t="s">
+        <v>11</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AR2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="BE2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="BP2" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BS2" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="BT2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="BU2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="BY2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BZ2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="CA2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="CC2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="CD2" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="CE2" s="1" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="CF2" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
         <v>54</v>
       </c>
-      <c r="B3" t="s">
+      <c r="CG2" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="CH2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="CI2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:87" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3">
         <v>31758</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K3">
         <v>94612</v>
       </c>
       <c r="L3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="S3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="T3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="U3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="X3" s="4">
         <v>10000000000</v>
@@ -1259,19 +1331,19 @@
         <v>46335</v>
       </c>
       <c r="Z3" s="6">
-        <v>46335.375</v>
+        <v>46335.416666666664</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AE3" s="4">
         <v>92626</v>
@@ -1279,158 +1351,167 @@
       <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
-      <c r="AI3" s="4" t="s">
-        <v>76</v>
+      <c r="AI3" s="8" t="s">
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AK3" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
-      <c r="AL3" t="s">
-        <v>79</v>
+      <c r="AL3" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="AM3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AN3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AO3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT3">
         <v>90001</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AU3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>88</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="BD3">
+        <v>90001</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>98</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>88</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP3">
+        <v>90001</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>104</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>107</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>108</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>109</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BX3" t="s">
         <v>83</v>
       </c>
-      <c r="AS3" t="s">
-        <v>84</v>
+      <c r="BY3" t="s">
+        <v>111</v>
       </c>
-      <c r="AT3" t="s">
-        <v>85</v>
+      <c r="BZ3" t="s">
+        <v>112</v>
       </c>
-      <c r="AU3" t="s">
-        <v>86</v>
+      <c r="CA3" t="s">
+        <v>94</v>
       </c>
-      <c r="AV3" t="s">
-        <v>87</v>
+      <c r="CB3" t="s">
+        <v>103</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="CC3" t="s">
         <v>88</v>
       </c>
-      <c r="AX3" t="s">
-        <v>89</v>
+      <c r="CD3" s="2" t="s">
+        <v>66</v>
       </c>
-      <c r="AY3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="BA3">
+      <c r="CE3">
         <v>90001</v>
       </c>
-      <c r="BB3" t="s">
-        <v>90</v>
+      <c r="CF3" t="s">
+        <v>105</v>
       </c>
-      <c r="BC3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>92</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>93</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BJ3" t="s">
+      <c r="CG3" t="s">
         <v>97</v>
       </c>
-      <c r="BK3" t="s">
-        <v>82</v>
+      <c r="CH3" t="s">
+        <v>113</v>
       </c>
-      <c r="BL3" s="2" t="s">
-        <v>62</v>
+      <c r="CI3" t="s">
+        <v>114</v>
       </c>
-      <c r="BM3">
-        <v>90001</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>99</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>102</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>103</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>77</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>105</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>82</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="CB3">
-        <v>90001</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>99</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>91</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>107</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1465,9 +1546,9 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
+      <c r="AI4" s="8"/>
+      <c r="AJ4" s="8"/>
+      <c r="AK4" s="8"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
@@ -1515,8 +1596,11 @@
       <c r="CD4" s="2"/>
       <c r="CE4" s="2"/>
       <c r="CF4" s="2"/>
-    </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG4" s="2"/>
+      <c r="CH4" s="2"/>
+      <c r="CI4" s="2"/>
+    </row>
+    <row r="5" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1551,9 +1635,9 @@
       <c r="AF5" s="2"/>
       <c r="AG5" s="2"/>
       <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
+      <c r="AI5" s="8"/>
+      <c r="AJ5" s="8"/>
+      <c r="AK5" s="8"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
@@ -1601,8 +1685,11 @@
       <c r="CD5" s="2"/>
       <c r="CE5" s="2"/>
       <c r="CF5" s="2"/>
-    </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG5" s="2"/>
+      <c r="CH5" s="2"/>
+      <c r="CI5" s="2"/>
+    </row>
+    <row r="6" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1637,9 +1724,9 @@
       <c r="AF6" s="2"/>
       <c r="AG6" s="2"/>
       <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
+      <c r="AI6" s="8"/>
+      <c r="AJ6" s="8"/>
+      <c r="AK6" s="8"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
@@ -1687,8 +1774,11 @@
       <c r="CD6" s="2"/>
       <c r="CE6" s="2"/>
       <c r="CF6" s="2"/>
-    </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG6" s="2"/>
+      <c r="CH6" s="2"/>
+      <c r="CI6" s="2"/>
+    </row>
+    <row r="7" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1723,9 +1813,9 @@
       <c r="AF7" s="2"/>
       <c r="AG7" s="2"/>
       <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
       <c r="AL7" s="2"/>
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
@@ -1773,8 +1863,11 @@
       <c r="CD7" s="2"/>
       <c r="CE7" s="2"/>
       <c r="CF7" s="2"/>
-    </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG7" s="2"/>
+      <c r="CH7" s="2"/>
+      <c r="CI7" s="2"/>
+    </row>
+    <row r="8" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1809,9 +1902,9 @@
       <c r="AF8" s="2"/>
       <c r="AG8" s="2"/>
       <c r="AH8" s="2"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
       <c r="AL8" s="2"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
@@ -1859,8 +1952,11 @@
       <c r="CD8" s="2"/>
       <c r="CE8" s="2"/>
       <c r="CF8" s="2"/>
-    </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG8" s="2"/>
+      <c r="CH8" s="2"/>
+      <c r="CI8" s="2"/>
+    </row>
+    <row r="9" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1895,9 +1991,9 @@
       <c r="AF9" s="2"/>
       <c r="AG9" s="2"/>
       <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
       <c r="AL9" s="2"/>
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
@@ -1945,8 +2041,11 @@
       <c r="CD9" s="2"/>
       <c r="CE9" s="2"/>
       <c r="CF9" s="2"/>
-    </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG9" s="2"/>
+      <c r="CH9" s="2"/>
+      <c r="CI9" s="2"/>
+    </row>
+    <row r="10" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1981,9 +2080,9 @@
       <c r="AF10" s="2"/>
       <c r="AG10" s="2"/>
       <c r="AH10" s="2"/>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-      <c r="AK10" s="2"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
       <c r="AL10" s="2"/>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
@@ -2031,8 +2130,11 @@
       <c r="CD10" s="2"/>
       <c r="CE10" s="2"/>
       <c r="CF10" s="2"/>
-    </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG10" s="2"/>
+      <c r="CH10" s="2"/>
+      <c r="CI10" s="2"/>
+    </row>
+    <row r="11" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2067,9 +2169,9 @@
       <c r="AF11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
+      <c r="AI11" s="8"/>
+      <c r="AJ11" s="8"/>
+      <c r="AK11" s="8"/>
       <c r="AL11" s="2"/>
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
@@ -2117,8 +2219,11 @@
       <c r="CD11" s="2"/>
       <c r="CE11" s="2"/>
       <c r="CF11" s="2"/>
-    </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG11" s="2"/>
+      <c r="CH11" s="2"/>
+      <c r="CI11" s="2"/>
+    </row>
+    <row r="12" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2153,9 +2258,9 @@
       <c r="AF12" s="2"/>
       <c r="AG12" s="2"/>
       <c r="AH12" s="2"/>
-      <c r="AI12" s="2"/>
-      <c r="AJ12" s="2"/>
-      <c r="AK12" s="2"/>
+      <c r="AI12" s="8"/>
+      <c r="AJ12" s="8"/>
+      <c r="AK12" s="8"/>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
@@ -2203,8 +2308,11 @@
       <c r="CD12" s="2"/>
       <c r="CE12" s="2"/>
       <c r="CF12" s="2"/>
-    </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG12" s="2"/>
+      <c r="CH12" s="2"/>
+      <c r="CI12" s="2"/>
+    </row>
+    <row r="13" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2239,9 +2347,9 @@
       <c r="AF13" s="2"/>
       <c r="AG13" s="2"/>
       <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
       <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
@@ -2289,8 +2397,11 @@
       <c r="CD13" s="2"/>
       <c r="CE13" s="2"/>
       <c r="CF13" s="2"/>
-    </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG13" s="2"/>
+      <c r="CH13" s="2"/>
+      <c r="CI13" s="2"/>
+    </row>
+    <row r="14" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2325,9 +2436,9 @@
       <c r="AF14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="8"/>
       <c r="AL14" s="2"/>
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
@@ -2375,8 +2486,11 @@
       <c r="CD14" s="2"/>
       <c r="CE14" s="2"/>
       <c r="CF14" s="2"/>
-    </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG14" s="2"/>
+      <c r="CH14" s="2"/>
+      <c r="CI14" s="2"/>
+    </row>
+    <row r="15" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2411,9 +2525,9 @@
       <c r="AF15" s="2"/>
       <c r="AG15" s="2"/>
       <c r="AH15" s="2"/>
-      <c r="AI15" s="2"/>
-      <c r="AJ15" s="2"/>
-      <c r="AK15" s="2"/>
+      <c r="AI15" s="8"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="8"/>
       <c r="AL15" s="2"/>
       <c r="AM15" s="2"/>
       <c r="AN15" s="2"/>
@@ -2461,8 +2575,11 @@
       <c r="CD15" s="2"/>
       <c r="CE15" s="2"/>
       <c r="CF15" s="2"/>
-    </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG15" s="2"/>
+      <c r="CH15" s="2"/>
+      <c r="CI15" s="2"/>
+    </row>
+    <row r="16" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2497,9 +2614,9 @@
       <c r="AF16" s="2"/>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="2"/>
+      <c r="AI16" s="8"/>
+      <c r="AJ16" s="8"/>
+      <c r="AK16" s="8"/>
       <c r="AL16" s="2"/>
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
@@ -2547,8 +2664,11 @@
       <c r="CD16" s="2"/>
       <c r="CE16" s="2"/>
       <c r="CF16" s="2"/>
-    </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG16" s="2"/>
+      <c r="CH16" s="2"/>
+      <c r="CI16" s="2"/>
+    </row>
+    <row r="17" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2583,9 +2703,9 @@
       <c r="AF17" s="2"/>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
       <c r="AL17" s="2"/>
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
@@ -2633,8 +2753,11 @@
       <c r="CD17" s="2"/>
       <c r="CE17" s="2"/>
       <c r="CF17" s="2"/>
-    </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG17" s="2"/>
+      <c r="CH17" s="2"/>
+      <c r="CI17" s="2"/>
+    </row>
+    <row r="18" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2669,9 +2792,9 @@
       <c r="AF18" s="2"/>
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
-      <c r="AI18" s="2"/>
-      <c r="AJ18" s="2"/>
-      <c r="AK18" s="2"/>
+      <c r="AI18" s="8"/>
+      <c r="AJ18" s="8"/>
+      <c r="AK18" s="8"/>
       <c r="AL18" s="2"/>
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
@@ -2719,8 +2842,11 @@
       <c r="CD18" s="2"/>
       <c r="CE18" s="2"/>
       <c r="CF18" s="2"/>
-    </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG18" s="2"/>
+      <c r="CH18" s="2"/>
+      <c r="CI18" s="2"/>
+    </row>
+    <row r="19" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2755,9 +2881,9 @@
       <c r="AF19" s="2"/>
       <c r="AG19" s="2"/>
       <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="8"/>
       <c r="AL19" s="2"/>
       <c r="AM19" s="2"/>
       <c r="AN19" s="2"/>
@@ -2805,8 +2931,11 @@
       <c r="CD19" s="2"/>
       <c r="CE19" s="2"/>
       <c r="CF19" s="2"/>
-    </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG19" s="2"/>
+      <c r="CH19" s="2"/>
+      <c r="CI19" s="2"/>
+    </row>
+    <row r="20" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2841,9 +2970,9 @@
       <c r="AF20" s="2"/>
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
+      <c r="AI20" s="8"/>
+      <c r="AJ20" s="8"/>
+      <c r="AK20" s="8"/>
       <c r="AL20" s="2"/>
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
@@ -2891,8 +3020,11 @@
       <c r="CD20" s="2"/>
       <c r="CE20" s="2"/>
       <c r="CF20" s="2"/>
-    </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG20" s="2"/>
+      <c r="CH20" s="2"/>
+      <c r="CI20" s="2"/>
+    </row>
+    <row r="21" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2927,9 +3059,9 @@
       <c r="AF21" s="2"/>
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
+      <c r="AI21" s="8"/>
+      <c r="AJ21" s="8"/>
+      <c r="AK21" s="8"/>
       <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
@@ -2977,8 +3109,11 @@
       <c r="CD21" s="2"/>
       <c r="CE21" s="2"/>
       <c r="CF21" s="2"/>
-    </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG21" s="2"/>
+      <c r="CH21" s="2"/>
+      <c r="CI21" s="2"/>
+    </row>
+    <row r="22" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -3013,9 +3148,9 @@
       <c r="AF22" s="2"/>
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
-      <c r="AI22" s="2"/>
-      <c r="AJ22" s="2"/>
-      <c r="AK22" s="2"/>
+      <c r="AI22" s="8"/>
+      <c r="AJ22" s="8"/>
+      <c r="AK22" s="8"/>
       <c r="AL22" s="2"/>
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
@@ -3063,8 +3198,11 @@
       <c r="CD22" s="2"/>
       <c r="CE22" s="2"/>
       <c r="CF22" s="2"/>
-    </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG22" s="2"/>
+      <c r="CH22" s="2"/>
+      <c r="CI22" s="2"/>
+    </row>
+    <row r="23" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3099,9 +3237,9 @@
       <c r="AF23" s="2"/>
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
+      <c r="AI23" s="8"/>
+      <c r="AJ23" s="8"/>
+      <c r="AK23" s="8"/>
       <c r="AL23" s="2"/>
       <c r="AM23" s="2"/>
       <c r="AN23" s="2"/>
@@ -3149,8 +3287,11 @@
       <c r="CD23" s="2"/>
       <c r="CE23" s="2"/>
       <c r="CF23" s="2"/>
-    </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG23" s="2"/>
+      <c r="CH23" s="2"/>
+      <c r="CI23" s="2"/>
+    </row>
+    <row r="24" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3185,9 +3326,9 @@
       <c r="AF24" s="2"/>
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
+      <c r="AI24" s="8"/>
+      <c r="AJ24" s="8"/>
+      <c r="AK24" s="8"/>
       <c r="AL24" s="2"/>
       <c r="AM24" s="2"/>
       <c r="AN24" s="2"/>
@@ -3235,8 +3376,11 @@
       <c r="CD24" s="2"/>
       <c r="CE24" s="2"/>
       <c r="CF24" s="2"/>
-    </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG24" s="2"/>
+      <c r="CH24" s="2"/>
+      <c r="CI24" s="2"/>
+    </row>
+    <row r="25" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3271,9 +3415,9 @@
       <c r="AF25" s="2"/>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
-      <c r="AI25" s="2"/>
-      <c r="AJ25" s="2"/>
-      <c r="AK25" s="2"/>
+      <c r="AI25" s="8"/>
+      <c r="AJ25" s="8"/>
+      <c r="AK25" s="8"/>
       <c r="AL25" s="2"/>
       <c r="AM25" s="2"/>
       <c r="AN25" s="2"/>
@@ -3321,8 +3465,11 @@
       <c r="CD25" s="2"/>
       <c r="CE25" s="2"/>
       <c r="CF25" s="2"/>
-    </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG25" s="2"/>
+      <c r="CH25" s="2"/>
+      <c r="CI25" s="2"/>
+    </row>
+    <row r="26" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3357,9 +3504,9 @@
       <c r="AF26" s="2"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
-      <c r="AI26" s="2"/>
-      <c r="AJ26" s="2"/>
-      <c r="AK26" s="2"/>
+      <c r="AI26" s="8"/>
+      <c r="AJ26" s="8"/>
+      <c r="AK26" s="8"/>
       <c r="AL26" s="2"/>
       <c r="AM26" s="2"/>
       <c r="AN26" s="2"/>
@@ -3407,8 +3554,11 @@
       <c r="CD26" s="2"/>
       <c r="CE26" s="2"/>
       <c r="CF26" s="2"/>
-    </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG26" s="2"/>
+      <c r="CH26" s="2"/>
+      <c r="CI26" s="2"/>
+    </row>
+    <row r="27" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3443,9 +3593,9 @@
       <c r="AF27" s="2"/>
       <c r="AG27" s="2"/>
       <c r="AH27" s="2"/>
-      <c r="AI27" s="2"/>
-      <c r="AJ27" s="2"/>
-      <c r="AK27" s="2"/>
+      <c r="AI27" s="8"/>
+      <c r="AJ27" s="8"/>
+      <c r="AK27" s="8"/>
       <c r="AL27" s="2"/>
       <c r="AM27" s="2"/>
       <c r="AN27" s="2"/>
@@ -3493,8 +3643,11 @@
       <c r="CD27" s="2"/>
       <c r="CE27" s="2"/>
       <c r="CF27" s="2"/>
-    </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG27" s="2"/>
+      <c r="CH27" s="2"/>
+      <c r="CI27" s="2"/>
+    </row>
+    <row r="28" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3529,9 +3682,9 @@
       <c r="AF28" s="2"/>
       <c r="AG28" s="2"/>
       <c r="AH28" s="2"/>
-      <c r="AI28" s="2"/>
-      <c r="AJ28" s="2"/>
-      <c r="AK28" s="2"/>
+      <c r="AI28" s="8"/>
+      <c r="AJ28" s="8"/>
+      <c r="AK28" s="8"/>
       <c r="AL28" s="2"/>
       <c r="AM28" s="2"/>
       <c r="AN28" s="2"/>
@@ -3579,8 +3732,11 @@
       <c r="CD28" s="2"/>
       <c r="CE28" s="2"/>
       <c r="CF28" s="2"/>
-    </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG28" s="2"/>
+      <c r="CH28" s="2"/>
+      <c r="CI28" s="2"/>
+    </row>
+    <row r="29" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3615,9 +3771,9 @@
       <c r="AF29" s="2"/>
       <c r="AG29" s="2"/>
       <c r="AH29" s="2"/>
-      <c r="AI29" s="2"/>
-      <c r="AJ29" s="2"/>
-      <c r="AK29" s="2"/>
+      <c r="AI29" s="8"/>
+      <c r="AJ29" s="8"/>
+      <c r="AK29" s="8"/>
       <c r="AL29" s="2"/>
       <c r="AM29" s="2"/>
       <c r="AN29" s="2"/>
@@ -3665,8 +3821,11 @@
       <c r="CD29" s="2"/>
       <c r="CE29" s="2"/>
       <c r="CF29" s="2"/>
-    </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG29" s="2"/>
+      <c r="CH29" s="2"/>
+      <c r="CI29" s="2"/>
+    </row>
+    <row r="30" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3701,9 +3860,9 @@
       <c r="AF30" s="2"/>
       <c r="AG30" s="2"/>
       <c r="AH30" s="2"/>
-      <c r="AI30" s="2"/>
-      <c r="AJ30" s="2"/>
-      <c r="AK30" s="2"/>
+      <c r="AI30" s="8"/>
+      <c r="AJ30" s="8"/>
+      <c r="AK30" s="8"/>
       <c r="AL30" s="2"/>
       <c r="AM30" s="2"/>
       <c r="AN30" s="2"/>
@@ -3751,8 +3910,11 @@
       <c r="CD30" s="2"/>
       <c r="CE30" s="2"/>
       <c r="CF30" s="2"/>
-    </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG30" s="2"/>
+      <c r="CH30" s="2"/>
+      <c r="CI30" s="2"/>
+    </row>
+    <row r="31" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3787,9 +3949,9 @@
       <c r="AF31" s="2"/>
       <c r="AG31" s="2"/>
       <c r="AH31" s="2"/>
-      <c r="AI31" s="2"/>
-      <c r="AJ31" s="2"/>
-      <c r="AK31" s="2"/>
+      <c r="AI31" s="8"/>
+      <c r="AJ31" s="8"/>
+      <c r="AK31" s="8"/>
       <c r="AL31" s="2"/>
       <c r="AM31" s="2"/>
       <c r="AN31" s="2"/>
@@ -3837,8 +3999,11 @@
       <c r="CD31" s="2"/>
       <c r="CE31" s="2"/>
       <c r="CF31" s="2"/>
-    </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG31" s="2"/>
+      <c r="CH31" s="2"/>
+      <c r="CI31" s="2"/>
+    </row>
+    <row r="32" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3873,9 +4038,9 @@
       <c r="AF32" s="2"/>
       <c r="AG32" s="2"/>
       <c r="AH32" s="2"/>
-      <c r="AI32" s="2"/>
-      <c r="AJ32" s="2"/>
-      <c r="AK32" s="2"/>
+      <c r="AI32" s="8"/>
+      <c r="AJ32" s="8"/>
+      <c r="AK32" s="8"/>
       <c r="AL32" s="2"/>
       <c r="AM32" s="2"/>
       <c r="AN32" s="2"/>
@@ -3923,8 +4088,11 @@
       <c r="CD32" s="2"/>
       <c r="CE32" s="2"/>
       <c r="CF32" s="2"/>
-    </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG32" s="2"/>
+      <c r="CH32" s="2"/>
+      <c r="CI32" s="2"/>
+    </row>
+    <row r="33" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3959,9 +4127,9 @@
       <c r="AF33" s="2"/>
       <c r="AG33" s="2"/>
       <c r="AH33" s="2"/>
-      <c r="AI33" s="2"/>
-      <c r="AJ33" s="2"/>
-      <c r="AK33" s="2"/>
+      <c r="AI33" s="8"/>
+      <c r="AJ33" s="8"/>
+      <c r="AK33" s="8"/>
       <c r="AL33" s="2"/>
       <c r="AM33" s="2"/>
       <c r="AN33" s="2"/>
@@ -4009,8 +4177,11 @@
       <c r="CD33" s="2"/>
       <c r="CE33" s="2"/>
       <c r="CF33" s="2"/>
-    </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG33" s="2"/>
+      <c r="CH33" s="2"/>
+      <c r="CI33" s="2"/>
+    </row>
+    <row r="34" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -4045,9 +4216,9 @@
       <c r="AF34" s="2"/>
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
-      <c r="AI34" s="2"/>
-      <c r="AJ34" s="2"/>
-      <c r="AK34" s="2"/>
+      <c r="AI34" s="8"/>
+      <c r="AJ34" s="8"/>
+      <c r="AK34" s="8"/>
       <c r="AL34" s="2"/>
       <c r="AM34" s="2"/>
       <c r="AN34" s="2"/>
@@ -4095,8 +4266,11 @@
       <c r="CD34" s="2"/>
       <c r="CE34" s="2"/>
       <c r="CF34" s="2"/>
-    </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG34" s="2"/>
+      <c r="CH34" s="2"/>
+      <c r="CI34" s="2"/>
+    </row>
+    <row r="35" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4131,9 +4305,9 @@
       <c r="AF35" s="2"/>
       <c r="AG35" s="2"/>
       <c r="AH35" s="2"/>
-      <c r="AI35" s="2"/>
-      <c r="AJ35" s="2"/>
-      <c r="AK35" s="2"/>
+      <c r="AI35" s="8"/>
+      <c r="AJ35" s="8"/>
+      <c r="AK35" s="8"/>
       <c r="AL35" s="2"/>
       <c r="AM35" s="2"/>
       <c r="AN35" s="2"/>
@@ -4181,8 +4355,11 @@
       <c r="CD35" s="2"/>
       <c r="CE35" s="2"/>
       <c r="CF35" s="2"/>
-    </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG35" s="2"/>
+      <c r="CH35" s="2"/>
+      <c r="CI35" s="2"/>
+    </row>
+    <row r="36" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4217,9 +4394,9 @@
       <c r="AF36" s="2"/>
       <c r="AG36" s="2"/>
       <c r="AH36" s="2"/>
-      <c r="AI36" s="2"/>
-      <c r="AJ36" s="2"/>
-      <c r="AK36" s="2"/>
+      <c r="AI36" s="8"/>
+      <c r="AJ36" s="8"/>
+      <c r="AK36" s="8"/>
       <c r="AL36" s="2"/>
       <c r="AM36" s="2"/>
       <c r="AN36" s="2"/>
@@ -4267,8 +4444,11 @@
       <c r="CD36" s="2"/>
       <c r="CE36" s="2"/>
       <c r="CF36" s="2"/>
-    </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG36" s="2"/>
+      <c r="CH36" s="2"/>
+      <c r="CI36" s="2"/>
+    </row>
+    <row r="37" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4303,9 +4483,9 @@
       <c r="AF37" s="2"/>
       <c r="AG37" s="2"/>
       <c r="AH37" s="2"/>
-      <c r="AI37" s="2"/>
-      <c r="AJ37" s="2"/>
-      <c r="AK37" s="2"/>
+      <c r="AI37" s="8"/>
+      <c r="AJ37" s="8"/>
+      <c r="AK37" s="8"/>
       <c r="AL37" s="2"/>
       <c r="AM37" s="2"/>
       <c r="AN37" s="2"/>
@@ -4353,8 +4533,11 @@
       <c r="CD37" s="2"/>
       <c r="CE37" s="2"/>
       <c r="CF37" s="2"/>
-    </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG37" s="2"/>
+      <c r="CH37" s="2"/>
+      <c r="CI37" s="2"/>
+    </row>
+    <row r="38" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4389,9 +4572,9 @@
       <c r="AF38" s="2"/>
       <c r="AG38" s="2"/>
       <c r="AH38" s="2"/>
-      <c r="AI38" s="2"/>
-      <c r="AJ38" s="2"/>
-      <c r="AK38" s="2"/>
+      <c r="AI38" s="8"/>
+      <c r="AJ38" s="8"/>
+      <c r="AK38" s="8"/>
       <c r="AL38" s="2"/>
       <c r="AM38" s="2"/>
       <c r="AN38" s="2"/>
@@ -4439,8 +4622,11 @@
       <c r="CD38" s="2"/>
       <c r="CE38" s="2"/>
       <c r="CF38" s="2"/>
-    </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG38" s="2"/>
+      <c r="CH38" s="2"/>
+      <c r="CI38" s="2"/>
+    </row>
+    <row r="39" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4475,9 +4661,9 @@
       <c r="AF39" s="2"/>
       <c r="AG39" s="2"/>
       <c r="AH39" s="2"/>
-      <c r="AI39" s="2"/>
-      <c r="AJ39" s="2"/>
-      <c r="AK39" s="2"/>
+      <c r="AI39" s="8"/>
+      <c r="AJ39" s="8"/>
+      <c r="AK39" s="8"/>
       <c r="AL39" s="2"/>
       <c r="AM39" s="2"/>
       <c r="AN39" s="2"/>
@@ -4525,8 +4711,11 @@
       <c r="CD39" s="2"/>
       <c r="CE39" s="2"/>
       <c r="CF39" s="2"/>
-    </row>
-    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG39" s="2"/>
+      <c r="CH39" s="2"/>
+      <c r="CI39" s="2"/>
+    </row>
+    <row r="40" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4561,9 +4750,9 @@
       <c r="AF40" s="2"/>
       <c r="AG40" s="2"/>
       <c r="AH40" s="2"/>
-      <c r="AI40" s="2"/>
-      <c r="AJ40" s="2"/>
-      <c r="AK40" s="2"/>
+      <c r="AI40" s="8"/>
+      <c r="AJ40" s="8"/>
+      <c r="AK40" s="8"/>
       <c r="AL40" s="2"/>
       <c r="AM40" s="2"/>
       <c r="AN40" s="2"/>
@@ -4611,8 +4800,11 @@
       <c r="CD40" s="2"/>
       <c r="CE40" s="2"/>
       <c r="CF40" s="2"/>
-    </row>
-    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG40" s="2"/>
+      <c r="CH40" s="2"/>
+      <c r="CI40" s="2"/>
+    </row>
+    <row r="41" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4647,9 +4839,9 @@
       <c r="AF41" s="2"/>
       <c r="AG41" s="2"/>
       <c r="AH41" s="2"/>
-      <c r="AI41" s="2"/>
-      <c r="AJ41" s="2"/>
-      <c r="AK41" s="2"/>
+      <c r="AI41" s="8"/>
+      <c r="AJ41" s="8"/>
+      <c r="AK41" s="8"/>
       <c r="AL41" s="2"/>
       <c r="AM41" s="2"/>
       <c r="AN41" s="2"/>
@@ -4697,8 +4889,11 @@
       <c r="CD41" s="2"/>
       <c r="CE41" s="2"/>
       <c r="CF41" s="2"/>
-    </row>
-    <row r="42" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG41" s="2"/>
+      <c r="CH41" s="2"/>
+      <c r="CI41" s="2"/>
+    </row>
+    <row r="42" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4733,9 +4928,9 @@
       <c r="AF42" s="2"/>
       <c r="AG42" s="2"/>
       <c r="AH42" s="2"/>
-      <c r="AI42" s="2"/>
-      <c r="AJ42" s="2"/>
-      <c r="AK42" s="2"/>
+      <c r="AI42" s="8"/>
+      <c r="AJ42" s="8"/>
+      <c r="AK42" s="8"/>
       <c r="AL42" s="2"/>
       <c r="AM42" s="2"/>
       <c r="AN42" s="2"/>
@@ -4783,8 +4978,11 @@
       <c r="CD42" s="2"/>
       <c r="CE42" s="2"/>
       <c r="CF42" s="2"/>
-    </row>
-    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG42" s="2"/>
+      <c r="CH42" s="2"/>
+      <c r="CI42" s="2"/>
+    </row>
+    <row r="43" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4819,9 +5017,9 @@
       <c r="AF43" s="2"/>
       <c r="AG43" s="2"/>
       <c r="AH43" s="2"/>
-      <c r="AI43" s="2"/>
-      <c r="AJ43" s="2"/>
-      <c r="AK43" s="2"/>
+      <c r="AI43" s="8"/>
+      <c r="AJ43" s="8"/>
+      <c r="AK43" s="8"/>
       <c r="AL43" s="2"/>
       <c r="AM43" s="2"/>
       <c r="AN43" s="2"/>
@@ -4869,8 +5067,11 @@
       <c r="CD43" s="2"/>
       <c r="CE43" s="2"/>
       <c r="CF43" s="2"/>
-    </row>
-    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG43" s="2"/>
+      <c r="CH43" s="2"/>
+      <c r="CI43" s="2"/>
+    </row>
+    <row r="44" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4905,9 +5106,9 @@
       <c r="AF44" s="2"/>
       <c r="AG44" s="2"/>
       <c r="AH44" s="2"/>
-      <c r="AI44" s="2"/>
-      <c r="AJ44" s="2"/>
-      <c r="AK44" s="2"/>
+      <c r="AI44" s="8"/>
+      <c r="AJ44" s="8"/>
+      <c r="AK44" s="8"/>
       <c r="AL44" s="2"/>
       <c r="AM44" s="2"/>
       <c r="AN44" s="2"/>
@@ -4955,8 +5156,11 @@
       <c r="CD44" s="2"/>
       <c r="CE44" s="2"/>
       <c r="CF44" s="2"/>
-    </row>
-    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG44" s="2"/>
+      <c r="CH44" s="2"/>
+      <c r="CI44" s="2"/>
+    </row>
+    <row r="45" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4991,9 +5195,9 @@
       <c r="AF45" s="2"/>
       <c r="AG45" s="2"/>
       <c r="AH45" s="2"/>
-      <c r="AI45" s="2"/>
-      <c r="AJ45" s="2"/>
-      <c r="AK45" s="2"/>
+      <c r="AI45" s="8"/>
+      <c r="AJ45" s="8"/>
+      <c r="AK45" s="8"/>
       <c r="AL45" s="2"/>
       <c r="AM45" s="2"/>
       <c r="AN45" s="2"/>
@@ -5041,8 +5245,11 @@
       <c r="CD45" s="2"/>
       <c r="CE45" s="2"/>
       <c r="CF45" s="2"/>
-    </row>
-    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG45" s="2"/>
+      <c r="CH45" s="2"/>
+      <c r="CI45" s="2"/>
+    </row>
+    <row r="46" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5077,9 +5284,9 @@
       <c r="AF46" s="2"/>
       <c r="AG46" s="2"/>
       <c r="AH46" s="2"/>
-      <c r="AI46" s="2"/>
-      <c r="AJ46" s="2"/>
-      <c r="AK46" s="2"/>
+      <c r="AI46" s="8"/>
+      <c r="AJ46" s="8"/>
+      <c r="AK46" s="8"/>
       <c r="AL46" s="2"/>
       <c r="AM46" s="2"/>
       <c r="AN46" s="2"/>
@@ -5127,8 +5334,11 @@
       <c r="CD46" s="2"/>
       <c r="CE46" s="2"/>
       <c r="CF46" s="2"/>
-    </row>
-    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG46" s="2"/>
+      <c r="CH46" s="2"/>
+      <c r="CI46" s="2"/>
+    </row>
+    <row r="47" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5163,9 +5373,9 @@
       <c r="AF47" s="2"/>
       <c r="AG47" s="2"/>
       <c r="AH47" s="2"/>
-      <c r="AI47" s="2"/>
-      <c r="AJ47" s="2"/>
-      <c r="AK47" s="2"/>
+      <c r="AI47" s="8"/>
+      <c r="AJ47" s="8"/>
+      <c r="AK47" s="8"/>
       <c r="AL47" s="2"/>
       <c r="AM47" s="2"/>
       <c r="AN47" s="2"/>
@@ -5213,8 +5423,11 @@
       <c r="CD47" s="2"/>
       <c r="CE47" s="2"/>
       <c r="CF47" s="2"/>
-    </row>
-    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG47" s="2"/>
+      <c r="CH47" s="2"/>
+      <c r="CI47" s="2"/>
+    </row>
+    <row r="48" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5249,9 +5462,9 @@
       <c r="AF48" s="2"/>
       <c r="AG48" s="2"/>
       <c r="AH48" s="2"/>
-      <c r="AI48" s="2"/>
-      <c r="AJ48" s="2"/>
-      <c r="AK48" s="2"/>
+      <c r="AI48" s="8"/>
+      <c r="AJ48" s="8"/>
+      <c r="AK48" s="8"/>
       <c r="AL48" s="2"/>
       <c r="AM48" s="2"/>
       <c r="AN48" s="2"/>
@@ -5299,8 +5512,11 @@
       <c r="CD48" s="2"/>
       <c r="CE48" s="2"/>
       <c r="CF48" s="2"/>
-    </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG48" s="2"/>
+      <c r="CH48" s="2"/>
+      <c r="CI48" s="2"/>
+    </row>
+    <row r="49" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -5335,9 +5551,9 @@
       <c r="AF49" s="2"/>
       <c r="AG49" s="2"/>
       <c r="AH49" s="2"/>
-      <c r="AI49" s="2"/>
-      <c r="AJ49" s="2"/>
-      <c r="AK49" s="2"/>
+      <c r="AI49" s="8"/>
+      <c r="AJ49" s="8"/>
+      <c r="AK49" s="8"/>
       <c r="AL49" s="2"/>
       <c r="AM49" s="2"/>
       <c r="AN49" s="2"/>
@@ -5385,8 +5601,11 @@
       <c r="CD49" s="2"/>
       <c r="CE49" s="2"/>
       <c r="CF49" s="2"/>
-    </row>
-    <row r="50" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG49" s="2"/>
+      <c r="CH49" s="2"/>
+      <c r="CI49" s="2"/>
+    </row>
+    <row r="50" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5421,9 +5640,9 @@
       <c r="AF50" s="2"/>
       <c r="AG50" s="2"/>
       <c r="AH50" s="2"/>
-      <c r="AI50" s="2"/>
-      <c r="AJ50" s="2"/>
-      <c r="AK50" s="2"/>
+      <c r="AI50" s="8"/>
+      <c r="AJ50" s="8"/>
+      <c r="AK50" s="8"/>
       <c r="AL50" s="2"/>
       <c r="AM50" s="2"/>
       <c r="AN50" s="2"/>
@@ -5471,8 +5690,11 @@
       <c r="CD50" s="2"/>
       <c r="CE50" s="2"/>
       <c r="CF50" s="2"/>
-    </row>
-    <row r="51" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG50" s="2"/>
+      <c r="CH50" s="2"/>
+      <c r="CI50" s="2"/>
+    </row>
+    <row r="51" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5507,9 +5729,9 @@
       <c r="AF51" s="2"/>
       <c r="AG51" s="2"/>
       <c r="AH51" s="2"/>
-      <c r="AI51" s="2"/>
-      <c r="AJ51" s="2"/>
-      <c r="AK51" s="2"/>
+      <c r="AI51" s="8"/>
+      <c r="AJ51" s="8"/>
+      <c r="AK51" s="8"/>
       <c r="AL51" s="2"/>
       <c r="AM51" s="2"/>
       <c r="AN51" s="2"/>
@@ -5557,8 +5779,11 @@
       <c r="CD51" s="2"/>
       <c r="CE51" s="2"/>
       <c r="CF51" s="2"/>
-    </row>
-    <row r="52" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG51" s="2"/>
+      <c r="CH51" s="2"/>
+      <c r="CI51" s="2"/>
+    </row>
+    <row r="52" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5593,9 +5818,9 @@
       <c r="AF52" s="2"/>
       <c r="AG52" s="2"/>
       <c r="AH52" s="2"/>
-      <c r="AI52" s="2"/>
-      <c r="AJ52" s="2"/>
-      <c r="AK52" s="2"/>
+      <c r="AI52" s="8"/>
+      <c r="AJ52" s="8"/>
+      <c r="AK52" s="8"/>
       <c r="AL52" s="2"/>
       <c r="AM52" s="2"/>
       <c r="AN52" s="2"/>
@@ -5643,8 +5868,11 @@
       <c r="CD52" s="2"/>
       <c r="CE52" s="2"/>
       <c r="CF52" s="2"/>
-    </row>
-    <row r="53" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG52" s="2"/>
+      <c r="CH52" s="2"/>
+      <c r="CI52" s="2"/>
+    </row>
+    <row r="53" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5679,9 +5907,9 @@
       <c r="AF53" s="2"/>
       <c r="AG53" s="2"/>
       <c r="AH53" s="2"/>
-      <c r="AI53" s="2"/>
-      <c r="AJ53" s="2"/>
-      <c r="AK53" s="2"/>
+      <c r="AI53" s="8"/>
+      <c r="AJ53" s="8"/>
+      <c r="AK53" s="8"/>
       <c r="AL53" s="2"/>
       <c r="AM53" s="2"/>
       <c r="AN53" s="2"/>
@@ -5729,8 +5957,11 @@
       <c r="CD53" s="2"/>
       <c r="CE53" s="2"/>
       <c r="CF53" s="2"/>
-    </row>
-    <row r="54" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG53" s="2"/>
+      <c r="CH53" s="2"/>
+      <c r="CI53" s="2"/>
+    </row>
+    <row r="54" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5765,9 +5996,9 @@
       <c r="AF54" s="2"/>
       <c r="AG54" s="2"/>
       <c r="AH54" s="2"/>
-      <c r="AI54" s="2"/>
-      <c r="AJ54" s="2"/>
-      <c r="AK54" s="2"/>
+      <c r="AI54" s="8"/>
+      <c r="AJ54" s="8"/>
+      <c r="AK54" s="8"/>
       <c r="AL54" s="2"/>
       <c r="AM54" s="2"/>
       <c r="AN54" s="2"/>
@@ -5815,8 +6046,11 @@
       <c r="CD54" s="2"/>
       <c r="CE54" s="2"/>
       <c r="CF54" s="2"/>
-    </row>
-    <row r="55" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG54" s="2"/>
+      <c r="CH54" s="2"/>
+      <c r="CI54" s="2"/>
+    </row>
+    <row r="55" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -5851,9 +6085,9 @@
       <c r="AF55" s="2"/>
       <c r="AG55" s="2"/>
       <c r="AH55" s="2"/>
-      <c r="AI55" s="2"/>
-      <c r="AJ55" s="2"/>
-      <c r="AK55" s="2"/>
+      <c r="AI55" s="8"/>
+      <c r="AJ55" s="8"/>
+      <c r="AK55" s="8"/>
       <c r="AL55" s="2"/>
       <c r="AM55" s="2"/>
       <c r="AN55" s="2"/>
@@ -5901,8 +6135,11 @@
       <c r="CD55" s="2"/>
       <c r="CE55" s="2"/>
       <c r="CF55" s="2"/>
-    </row>
-    <row r="56" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG55" s="2"/>
+      <c r="CH55" s="2"/>
+      <c r="CI55" s="2"/>
+    </row>
+    <row r="56" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -5937,9 +6174,9 @@
       <c r="AF56" s="2"/>
       <c r="AG56" s="2"/>
       <c r="AH56" s="2"/>
-      <c r="AI56" s="2"/>
-      <c r="AJ56" s="2"/>
-      <c r="AK56" s="2"/>
+      <c r="AI56" s="8"/>
+      <c r="AJ56" s="8"/>
+      <c r="AK56" s="8"/>
       <c r="AL56" s="2"/>
       <c r="AM56" s="2"/>
       <c r="AN56" s="2"/>
@@ -5987,8 +6224,11 @@
       <c r="CD56" s="2"/>
       <c r="CE56" s="2"/>
       <c r="CF56" s="2"/>
-    </row>
-    <row r="57" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG56" s="2"/>
+      <c r="CH56" s="2"/>
+      <c r="CI56" s="2"/>
+    </row>
+    <row r="57" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -6023,9 +6263,9 @@
       <c r="AF57" s="2"/>
       <c r="AG57" s="2"/>
       <c r="AH57" s="2"/>
-      <c r="AI57" s="2"/>
-      <c r="AJ57" s="2"/>
-      <c r="AK57" s="2"/>
+      <c r="AI57" s="8"/>
+      <c r="AJ57" s="8"/>
+      <c r="AK57" s="8"/>
       <c r="AL57" s="2"/>
       <c r="AM57" s="2"/>
       <c r="AN57" s="2"/>
@@ -6073,8 +6313,11 @@
       <c r="CD57" s="2"/>
       <c r="CE57" s="2"/>
       <c r="CF57" s="2"/>
-    </row>
-    <row r="58" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG57" s="2"/>
+      <c r="CH57" s="2"/>
+      <c r="CI57" s="2"/>
+    </row>
+    <row r="58" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -6109,9 +6352,9 @@
       <c r="AF58" s="2"/>
       <c r="AG58" s="2"/>
       <c r="AH58" s="2"/>
-      <c r="AI58" s="2"/>
-      <c r="AJ58" s="2"/>
-      <c r="AK58" s="2"/>
+      <c r="AI58" s="8"/>
+      <c r="AJ58" s="8"/>
+      <c r="AK58" s="8"/>
       <c r="AL58" s="2"/>
       <c r="AM58" s="2"/>
       <c r="AN58" s="2"/>
@@ -6159,8 +6402,11 @@
       <c r="CD58" s="2"/>
       <c r="CE58" s="2"/>
       <c r="CF58" s="2"/>
-    </row>
-    <row r="59" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG58" s="2"/>
+      <c r="CH58" s="2"/>
+      <c r="CI58" s="2"/>
+    </row>
+    <row r="59" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -6195,9 +6441,9 @@
       <c r="AF59" s="2"/>
       <c r="AG59" s="2"/>
       <c r="AH59" s="2"/>
-      <c r="AI59" s="2"/>
-      <c r="AJ59" s="2"/>
-      <c r="AK59" s="2"/>
+      <c r="AI59" s="8"/>
+      <c r="AJ59" s="8"/>
+      <c r="AK59" s="8"/>
       <c r="AL59" s="2"/>
       <c r="AM59" s="2"/>
       <c r="AN59" s="2"/>
@@ -6245,8 +6491,11 @@
       <c r="CD59" s="2"/>
       <c r="CE59" s="2"/>
       <c r="CF59" s="2"/>
-    </row>
-    <row r="60" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG59" s="2"/>
+      <c r="CH59" s="2"/>
+      <c r="CI59" s="2"/>
+    </row>
+    <row r="60" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -6281,9 +6530,9 @@
       <c r="AF60" s="2"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
-      <c r="AI60" s="2"/>
-      <c r="AJ60" s="2"/>
-      <c r="AK60" s="2"/>
+      <c r="AI60" s="8"/>
+      <c r="AJ60" s="8"/>
+      <c r="AK60" s="8"/>
       <c r="AL60" s="2"/>
       <c r="AM60" s="2"/>
       <c r="AN60" s="2"/>
@@ -6331,8 +6580,11 @@
       <c r="CD60" s="2"/>
       <c r="CE60" s="2"/>
       <c r="CF60" s="2"/>
-    </row>
-    <row r="61" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG60" s="2"/>
+      <c r="CH60" s="2"/>
+      <c r="CI60" s="2"/>
+    </row>
+    <row r="61" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -6367,9 +6619,9 @@
       <c r="AF61" s="2"/>
       <c r="AG61" s="2"/>
       <c r="AH61" s="2"/>
-      <c r="AI61" s="2"/>
-      <c r="AJ61" s="2"/>
-      <c r="AK61" s="2"/>
+      <c r="AI61" s="8"/>
+      <c r="AJ61" s="8"/>
+      <c r="AK61" s="8"/>
       <c r="AL61" s="2"/>
       <c r="AM61" s="2"/>
       <c r="AN61" s="2"/>
@@ -6417,8 +6669,11 @@
       <c r="CD61" s="2"/>
       <c r="CE61" s="2"/>
       <c r="CF61" s="2"/>
-    </row>
-    <row r="62" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG61" s="2"/>
+      <c r="CH61" s="2"/>
+      <c r="CI61" s="2"/>
+    </row>
+    <row r="62" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -6453,9 +6708,9 @@
       <c r="AF62" s="2"/>
       <c r="AG62" s="2"/>
       <c r="AH62" s="2"/>
-      <c r="AI62" s="2"/>
-      <c r="AJ62" s="2"/>
-      <c r="AK62" s="2"/>
+      <c r="AI62" s="8"/>
+      <c r="AJ62" s="8"/>
+      <c r="AK62" s="8"/>
       <c r="AL62" s="2"/>
       <c r="AM62" s="2"/>
       <c r="AN62" s="2"/>
@@ -6503,8 +6758,11 @@
       <c r="CD62" s="2"/>
       <c r="CE62" s="2"/>
       <c r="CF62" s="2"/>
-    </row>
-    <row r="63" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG62" s="2"/>
+      <c r="CH62" s="2"/>
+      <c r="CI62" s="2"/>
+    </row>
+    <row r="63" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -6539,9 +6797,9 @@
       <c r="AF63" s="2"/>
       <c r="AG63" s="2"/>
       <c r="AH63" s="2"/>
-      <c r="AI63" s="2"/>
-      <c r="AJ63" s="2"/>
-      <c r="AK63" s="2"/>
+      <c r="AI63" s="8"/>
+      <c r="AJ63" s="8"/>
+      <c r="AK63" s="8"/>
       <c r="AL63" s="2"/>
       <c r="AM63" s="2"/>
       <c r="AN63" s="2"/>
@@ -6589,8 +6847,11 @@
       <c r="CD63" s="2"/>
       <c r="CE63" s="2"/>
       <c r="CF63" s="2"/>
-    </row>
-    <row r="64" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG63" s="2"/>
+      <c r="CH63" s="2"/>
+      <c r="CI63" s="2"/>
+    </row>
+    <row r="64" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -6625,9 +6886,9 @@
       <c r="AF64" s="2"/>
       <c r="AG64" s="2"/>
       <c r="AH64" s="2"/>
-      <c r="AI64" s="2"/>
-      <c r="AJ64" s="2"/>
-      <c r="AK64" s="2"/>
+      <c r="AI64" s="8"/>
+      <c r="AJ64" s="8"/>
+      <c r="AK64" s="8"/>
       <c r="AL64" s="2"/>
       <c r="AM64" s="2"/>
       <c r="AN64" s="2"/>
@@ -6675,8 +6936,11 @@
       <c r="CD64" s="2"/>
       <c r="CE64" s="2"/>
       <c r="CF64" s="2"/>
-    </row>
-    <row r="65" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG64" s="2"/>
+      <c r="CH64" s="2"/>
+      <c r="CI64" s="2"/>
+    </row>
+    <row r="65" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -6711,9 +6975,9 @@
       <c r="AF65" s="2"/>
       <c r="AG65" s="2"/>
       <c r="AH65" s="2"/>
-      <c r="AI65" s="2"/>
-      <c r="AJ65" s="2"/>
-      <c r="AK65" s="2"/>
+      <c r="AI65" s="8"/>
+      <c r="AJ65" s="8"/>
+      <c r="AK65" s="8"/>
       <c r="AL65" s="2"/>
       <c r="AM65" s="2"/>
       <c r="AN65" s="2"/>
@@ -6761,8 +7025,11 @@
       <c r="CD65" s="2"/>
       <c r="CE65" s="2"/>
       <c r="CF65" s="2"/>
-    </row>
-    <row r="66" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG65" s="2"/>
+      <c r="CH65" s="2"/>
+      <c r="CI65" s="2"/>
+    </row>
+    <row r="66" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -6797,9 +7064,9 @@
       <c r="AF66" s="2"/>
       <c r="AG66" s="2"/>
       <c r="AH66" s="2"/>
-      <c r="AI66" s="2"/>
-      <c r="AJ66" s="2"/>
-      <c r="AK66" s="2"/>
+      <c r="AI66" s="8"/>
+      <c r="AJ66" s="8"/>
+      <c r="AK66" s="8"/>
       <c r="AL66" s="2"/>
       <c r="AM66" s="2"/>
       <c r="AN66" s="2"/>
@@ -6847,8 +7114,11 @@
       <c r="CD66" s="2"/>
       <c r="CE66" s="2"/>
       <c r="CF66" s="2"/>
-    </row>
-    <row r="67" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG66" s="2"/>
+      <c r="CH66" s="2"/>
+      <c r="CI66" s="2"/>
+    </row>
+    <row r="67" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6883,9 +7153,9 @@
       <c r="AF67" s="2"/>
       <c r="AG67" s="2"/>
       <c r="AH67" s="2"/>
-      <c r="AI67" s="2"/>
-      <c r="AJ67" s="2"/>
-      <c r="AK67" s="2"/>
+      <c r="AI67" s="8"/>
+      <c r="AJ67" s="8"/>
+      <c r="AK67" s="8"/>
       <c r="AL67" s="2"/>
       <c r="AM67" s="2"/>
       <c r="AN67" s="2"/>
@@ -6933,8 +7203,11 @@
       <c r="CD67" s="2"/>
       <c r="CE67" s="2"/>
       <c r="CF67" s="2"/>
-    </row>
-    <row r="68" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG67" s="2"/>
+      <c r="CH67" s="2"/>
+      <c r="CI67" s="2"/>
+    </row>
+    <row r="68" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -6969,9 +7242,9 @@
       <c r="AF68" s="2"/>
       <c r="AG68" s="2"/>
       <c r="AH68" s="2"/>
-      <c r="AI68" s="2"/>
-      <c r="AJ68" s="2"/>
-      <c r="AK68" s="2"/>
+      <c r="AI68" s="8"/>
+      <c r="AJ68" s="8"/>
+      <c r="AK68" s="8"/>
       <c r="AL68" s="2"/>
       <c r="AM68" s="2"/>
       <c r="AN68" s="2"/>
@@ -7019,8 +7292,11 @@
       <c r="CD68" s="2"/>
       <c r="CE68" s="2"/>
       <c r="CF68" s="2"/>
-    </row>
-    <row r="69" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG68" s="2"/>
+      <c r="CH68" s="2"/>
+      <c r="CI68" s="2"/>
+    </row>
+    <row r="69" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -7055,9 +7331,9 @@
       <c r="AF69" s="2"/>
       <c r="AG69" s="2"/>
       <c r="AH69" s="2"/>
-      <c r="AI69" s="2"/>
-      <c r="AJ69" s="2"/>
-      <c r="AK69" s="2"/>
+      <c r="AI69" s="8"/>
+      <c r="AJ69" s="8"/>
+      <c r="AK69" s="8"/>
       <c r="AL69" s="2"/>
       <c r="AM69" s="2"/>
       <c r="AN69" s="2"/>
@@ -7105,8 +7381,11 @@
       <c r="CD69" s="2"/>
       <c r="CE69" s="2"/>
       <c r="CF69" s="2"/>
-    </row>
-    <row r="70" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG69" s="2"/>
+      <c r="CH69" s="2"/>
+      <c r="CI69" s="2"/>
+    </row>
+    <row r="70" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -7141,9 +7420,9 @@
       <c r="AF70" s="2"/>
       <c r="AG70" s="2"/>
       <c r="AH70" s="2"/>
-      <c r="AI70" s="2"/>
-      <c r="AJ70" s="2"/>
-      <c r="AK70" s="2"/>
+      <c r="AI70" s="8"/>
+      <c r="AJ70" s="8"/>
+      <c r="AK70" s="8"/>
       <c r="AL70" s="2"/>
       <c r="AM70" s="2"/>
       <c r="AN70" s="2"/>
@@ -7191,8 +7470,11 @@
       <c r="CD70" s="2"/>
       <c r="CE70" s="2"/>
       <c r="CF70" s="2"/>
-    </row>
-    <row r="71" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG70" s="2"/>
+      <c r="CH70" s="2"/>
+      <c r="CI70" s="2"/>
+    </row>
+    <row r="71" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -7227,9 +7509,9 @@
       <c r="AF71" s="2"/>
       <c r="AG71" s="2"/>
       <c r="AH71" s="2"/>
-      <c r="AI71" s="2"/>
-      <c r="AJ71" s="2"/>
-      <c r="AK71" s="2"/>
+      <c r="AI71" s="8"/>
+      <c r="AJ71" s="8"/>
+      <c r="AK71" s="8"/>
       <c r="AL71" s="2"/>
       <c r="AM71" s="2"/>
       <c r="AN71" s="2"/>
@@ -7277,8 +7559,11 @@
       <c r="CD71" s="2"/>
       <c r="CE71" s="2"/>
       <c r="CF71" s="2"/>
-    </row>
-    <row r="72" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG71" s="2"/>
+      <c r="CH71" s="2"/>
+      <c r="CI71" s="2"/>
+    </row>
+    <row r="72" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -7313,9 +7598,9 @@
       <c r="AF72" s="2"/>
       <c r="AG72" s="2"/>
       <c r="AH72" s="2"/>
-      <c r="AI72" s="2"/>
-      <c r="AJ72" s="2"/>
-      <c r="AK72" s="2"/>
+      <c r="AI72" s="8"/>
+      <c r="AJ72" s="8"/>
+      <c r="AK72" s="8"/>
       <c r="AL72" s="2"/>
       <c r="AM72" s="2"/>
       <c r="AN72" s="2"/>
@@ -7363,8 +7648,11 @@
       <c r="CD72" s="2"/>
       <c r="CE72" s="2"/>
       <c r="CF72" s="2"/>
-    </row>
-    <row r="73" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG72" s="2"/>
+      <c r="CH72" s="2"/>
+      <c r="CI72" s="2"/>
+    </row>
+    <row r="73" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -7399,9 +7687,9 @@
       <c r="AF73" s="2"/>
       <c r="AG73" s="2"/>
       <c r="AH73" s="2"/>
-      <c r="AI73" s="2"/>
-      <c r="AJ73" s="2"/>
-      <c r="AK73" s="2"/>
+      <c r="AI73" s="8"/>
+      <c r="AJ73" s="8"/>
+      <c r="AK73" s="8"/>
       <c r="AL73" s="2"/>
       <c r="AM73" s="2"/>
       <c r="AN73" s="2"/>
@@ -7449,8 +7737,11 @@
       <c r="CD73" s="2"/>
       <c r="CE73" s="2"/>
       <c r="CF73" s="2"/>
-    </row>
-    <row r="74" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG73" s="2"/>
+      <c r="CH73" s="2"/>
+      <c r="CI73" s="2"/>
+    </row>
+    <row r="74" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -7485,9 +7776,9 @@
       <c r="AF74" s="2"/>
       <c r="AG74" s="2"/>
       <c r="AH74" s="2"/>
-      <c r="AI74" s="2"/>
-      <c r="AJ74" s="2"/>
-      <c r="AK74" s="2"/>
+      <c r="AI74" s="8"/>
+      <c r="AJ74" s="8"/>
+      <c r="AK74" s="8"/>
       <c r="AL74" s="2"/>
       <c r="AM74" s="2"/>
       <c r="AN74" s="2"/>
@@ -7535,8 +7826,11 @@
       <c r="CD74" s="2"/>
       <c r="CE74" s="2"/>
       <c r="CF74" s="2"/>
-    </row>
-    <row r="75" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG74" s="2"/>
+      <c r="CH74" s="2"/>
+      <c r="CI74" s="2"/>
+    </row>
+    <row r="75" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -7571,9 +7865,9 @@
       <c r="AF75" s="2"/>
       <c r="AG75" s="2"/>
       <c r="AH75" s="2"/>
-      <c r="AI75" s="2"/>
-      <c r="AJ75" s="2"/>
-      <c r="AK75" s="2"/>
+      <c r="AI75" s="8"/>
+      <c r="AJ75" s="8"/>
+      <c r="AK75" s="8"/>
       <c r="AL75" s="2"/>
       <c r="AM75" s="2"/>
       <c r="AN75" s="2"/>
@@ -7621,8 +7915,11 @@
       <c r="CD75" s="2"/>
       <c r="CE75" s="2"/>
       <c r="CF75" s="2"/>
-    </row>
-    <row r="76" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG75" s="2"/>
+      <c r="CH75" s="2"/>
+      <c r="CI75" s="2"/>
+    </row>
+    <row r="76" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -7657,9 +7954,9 @@
       <c r="AF76" s="2"/>
       <c r="AG76" s="2"/>
       <c r="AH76" s="2"/>
-      <c r="AI76" s="2"/>
-      <c r="AJ76" s="2"/>
-      <c r="AK76" s="2"/>
+      <c r="AI76" s="8"/>
+      <c r="AJ76" s="8"/>
+      <c r="AK76" s="8"/>
       <c r="AL76" s="2"/>
       <c r="AM76" s="2"/>
       <c r="AN76" s="2"/>
@@ -7707,8 +8004,11 @@
       <c r="CD76" s="2"/>
       <c r="CE76" s="2"/>
       <c r="CF76" s="2"/>
-    </row>
-    <row r="77" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG76" s="2"/>
+      <c r="CH76" s="2"/>
+      <c r="CI76" s="2"/>
+    </row>
+    <row r="77" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -7743,9 +8043,9 @@
       <c r="AF77" s="2"/>
       <c r="AG77" s="2"/>
       <c r="AH77" s="2"/>
-      <c r="AI77" s="2"/>
-      <c r="AJ77" s="2"/>
-      <c r="AK77" s="2"/>
+      <c r="AI77" s="8"/>
+      <c r="AJ77" s="8"/>
+      <c r="AK77" s="8"/>
       <c r="AL77" s="2"/>
       <c r="AM77" s="2"/>
       <c r="AN77" s="2"/>
@@ -7793,8 +8093,11 @@
       <c r="CD77" s="2"/>
       <c r="CE77" s="2"/>
       <c r="CF77" s="2"/>
-    </row>
-    <row r="78" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG77" s="2"/>
+      <c r="CH77" s="2"/>
+      <c r="CI77" s="2"/>
+    </row>
+    <row r="78" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -7829,9 +8132,9 @@
       <c r="AF78" s="2"/>
       <c r="AG78" s="2"/>
       <c r="AH78" s="2"/>
-      <c r="AI78" s="2"/>
-      <c r="AJ78" s="2"/>
-      <c r="AK78" s="2"/>
+      <c r="AI78" s="8"/>
+      <c r="AJ78" s="8"/>
+      <c r="AK78" s="8"/>
       <c r="AL78" s="2"/>
       <c r="AM78" s="2"/>
       <c r="AN78" s="2"/>
@@ -7879,8 +8182,11 @@
       <c r="CD78" s="2"/>
       <c r="CE78" s="2"/>
       <c r="CF78" s="2"/>
-    </row>
-    <row r="79" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG78" s="2"/>
+      <c r="CH78" s="2"/>
+      <c r="CI78" s="2"/>
+    </row>
+    <row r="79" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -7915,9 +8221,9 @@
       <c r="AF79" s="2"/>
       <c r="AG79" s="2"/>
       <c r="AH79" s="2"/>
-      <c r="AI79" s="2"/>
-      <c r="AJ79" s="2"/>
-      <c r="AK79" s="2"/>
+      <c r="AI79" s="8"/>
+      <c r="AJ79" s="8"/>
+      <c r="AK79" s="8"/>
       <c r="AL79" s="2"/>
       <c r="AM79" s="2"/>
       <c r="AN79" s="2"/>
@@ -7965,8 +8271,11 @@
       <c r="CD79" s="2"/>
       <c r="CE79" s="2"/>
       <c r="CF79" s="2"/>
-    </row>
-    <row r="80" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG79" s="2"/>
+      <c r="CH79" s="2"/>
+      <c r="CI79" s="2"/>
+    </row>
+    <row r="80" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -8001,9 +8310,9 @@
       <c r="AF80" s="2"/>
       <c r="AG80" s="2"/>
       <c r="AH80" s="2"/>
-      <c r="AI80" s="2"/>
-      <c r="AJ80" s="2"/>
-      <c r="AK80" s="2"/>
+      <c r="AI80" s="8"/>
+      <c r="AJ80" s="8"/>
+      <c r="AK80" s="8"/>
       <c r="AL80" s="2"/>
       <c r="AM80" s="2"/>
       <c r="AN80" s="2"/>
@@ -8051,8 +8360,11 @@
       <c r="CD80" s="2"/>
       <c r="CE80" s="2"/>
       <c r="CF80" s="2"/>
-    </row>
-    <row r="81" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG80" s="2"/>
+      <c r="CH80" s="2"/>
+      <c r="CI80" s="2"/>
+    </row>
+    <row r="81" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -8087,9 +8399,9 @@
       <c r="AF81" s="2"/>
       <c r="AG81" s="2"/>
       <c r="AH81" s="2"/>
-      <c r="AI81" s="2"/>
-      <c r="AJ81" s="2"/>
-      <c r="AK81" s="2"/>
+      <c r="AI81" s="8"/>
+      <c r="AJ81" s="8"/>
+      <c r="AK81" s="8"/>
       <c r="AL81" s="2"/>
       <c r="AM81" s="2"/>
       <c r="AN81" s="2"/>
@@ -8137,8 +8449,11 @@
       <c r="CD81" s="2"/>
       <c r="CE81" s="2"/>
       <c r="CF81" s="2"/>
-    </row>
-    <row r="82" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG81" s="2"/>
+      <c r="CH81" s="2"/>
+      <c r="CI81" s="2"/>
+    </row>
+    <row r="82" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -8173,9 +8488,9 @@
       <c r="AF82" s="2"/>
       <c r="AG82" s="2"/>
       <c r="AH82" s="2"/>
-      <c r="AI82" s="2"/>
-      <c r="AJ82" s="2"/>
-      <c r="AK82" s="2"/>
+      <c r="AI82" s="8"/>
+      <c r="AJ82" s="8"/>
+      <c r="AK82" s="8"/>
       <c r="AL82" s="2"/>
       <c r="AM82" s="2"/>
       <c r="AN82" s="2"/>
@@ -8223,8 +8538,11 @@
       <c r="CD82" s="2"/>
       <c r="CE82" s="2"/>
       <c r="CF82" s="2"/>
-    </row>
-    <row r="83" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG82" s="2"/>
+      <c r="CH82" s="2"/>
+      <c r="CI82" s="2"/>
+    </row>
+    <row r="83" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -8259,9 +8577,9 @@
       <c r="AF83" s="2"/>
       <c r="AG83" s="2"/>
       <c r="AH83" s="2"/>
-      <c r="AI83" s="2"/>
-      <c r="AJ83" s="2"/>
-      <c r="AK83" s="2"/>
+      <c r="AI83" s="8"/>
+      <c r="AJ83" s="8"/>
+      <c r="AK83" s="8"/>
       <c r="AL83" s="2"/>
       <c r="AM83" s="2"/>
       <c r="AN83" s="2"/>
@@ -8309,8 +8627,11 @@
       <c r="CD83" s="2"/>
       <c r="CE83" s="2"/>
       <c r="CF83" s="2"/>
-    </row>
-    <row r="84" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG83" s="2"/>
+      <c r="CH83" s="2"/>
+      <c r="CI83" s="2"/>
+    </row>
+    <row r="84" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -8345,9 +8666,9 @@
       <c r="AF84" s="2"/>
       <c r="AG84" s="2"/>
       <c r="AH84" s="2"/>
-      <c r="AI84" s="2"/>
-      <c r="AJ84" s="2"/>
-      <c r="AK84" s="2"/>
+      <c r="AI84" s="8"/>
+      <c r="AJ84" s="8"/>
+      <c r="AK84" s="8"/>
       <c r="AL84" s="2"/>
       <c r="AM84" s="2"/>
       <c r="AN84" s="2"/>
@@ -8395,8 +8716,11 @@
       <c r="CD84" s="2"/>
       <c r="CE84" s="2"/>
       <c r="CF84" s="2"/>
-    </row>
-    <row r="85" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG84" s="2"/>
+      <c r="CH84" s="2"/>
+      <c r="CI84" s="2"/>
+    </row>
+    <row r="85" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -8431,9 +8755,9 @@
       <c r="AF85" s="2"/>
       <c r="AG85" s="2"/>
       <c r="AH85" s="2"/>
-      <c r="AI85" s="2"/>
-      <c r="AJ85" s="2"/>
-      <c r="AK85" s="2"/>
+      <c r="AI85" s="8"/>
+      <c r="AJ85" s="8"/>
+      <c r="AK85" s="8"/>
       <c r="AL85" s="2"/>
       <c r="AM85" s="2"/>
       <c r="AN85" s="2"/>
@@ -8481,8 +8805,11 @@
       <c r="CD85" s="2"/>
       <c r="CE85" s="2"/>
       <c r="CF85" s="2"/>
-    </row>
-    <row r="86" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG85" s="2"/>
+      <c r="CH85" s="2"/>
+      <c r="CI85" s="2"/>
+    </row>
+    <row r="86" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -8517,9 +8844,9 @@
       <c r="AF86" s="2"/>
       <c r="AG86" s="2"/>
       <c r="AH86" s="2"/>
-      <c r="AI86" s="2"/>
-      <c r="AJ86" s="2"/>
-      <c r="AK86" s="2"/>
+      <c r="AI86" s="8"/>
+      <c r="AJ86" s="8"/>
+      <c r="AK86" s="8"/>
       <c r="AL86" s="2"/>
       <c r="AM86" s="2"/>
       <c r="AN86" s="2"/>
@@ -8567,8 +8894,11 @@
       <c r="CD86" s="2"/>
       <c r="CE86" s="2"/>
       <c r="CF86" s="2"/>
-    </row>
-    <row r="87" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG86" s="2"/>
+      <c r="CH86" s="2"/>
+      <c r="CI86" s="2"/>
+    </row>
+    <row r="87" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -8603,9 +8933,9 @@
       <c r="AF87" s="2"/>
       <c r="AG87" s="2"/>
       <c r="AH87" s="2"/>
-      <c r="AI87" s="2"/>
-      <c r="AJ87" s="2"/>
-      <c r="AK87" s="2"/>
+      <c r="AI87" s="8"/>
+      <c r="AJ87" s="8"/>
+      <c r="AK87" s="8"/>
       <c r="AL87" s="2"/>
       <c r="AM87" s="2"/>
       <c r="AN87" s="2"/>
@@ -8653,8 +8983,11 @@
       <c r="CD87" s="2"/>
       <c r="CE87" s="2"/>
       <c r="CF87" s="2"/>
-    </row>
-    <row r="88" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG87" s="2"/>
+      <c r="CH87" s="2"/>
+      <c r="CI87" s="2"/>
+    </row>
+    <row r="88" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -8689,9 +9022,9 @@
       <c r="AF88" s="2"/>
       <c r="AG88" s="2"/>
       <c r="AH88" s="2"/>
-      <c r="AI88" s="2"/>
-      <c r="AJ88" s="2"/>
-      <c r="AK88" s="2"/>
+      <c r="AI88" s="8"/>
+      <c r="AJ88" s="8"/>
+      <c r="AK88" s="8"/>
       <c r="AL88" s="2"/>
       <c r="AM88" s="2"/>
       <c r="AN88" s="2"/>
@@ -8739,8 +9072,11 @@
       <c r="CD88" s="2"/>
       <c r="CE88" s="2"/>
       <c r="CF88" s="2"/>
-    </row>
-    <row r="89" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG88" s="2"/>
+      <c r="CH88" s="2"/>
+      <c r="CI88" s="2"/>
+    </row>
+    <row r="89" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -8775,9 +9111,9 @@
       <c r="AF89" s="2"/>
       <c r="AG89" s="2"/>
       <c r="AH89" s="2"/>
-      <c r="AI89" s="2"/>
-      <c r="AJ89" s="2"/>
-      <c r="AK89" s="2"/>
+      <c r="AI89" s="8"/>
+      <c r="AJ89" s="8"/>
+      <c r="AK89" s="8"/>
       <c r="AL89" s="2"/>
       <c r="AM89" s="2"/>
       <c r="AN89" s="2"/>
@@ -8825,8 +9161,11 @@
       <c r="CD89" s="2"/>
       <c r="CE89" s="2"/>
       <c r="CF89" s="2"/>
-    </row>
-    <row r="90" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG89" s="2"/>
+      <c r="CH89" s="2"/>
+      <c r="CI89" s="2"/>
+    </row>
+    <row r="90" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -8861,9 +9200,9 @@
       <c r="AF90" s="2"/>
       <c r="AG90" s="2"/>
       <c r="AH90" s="2"/>
-      <c r="AI90" s="2"/>
-      <c r="AJ90" s="2"/>
-      <c r="AK90" s="2"/>
+      <c r="AI90" s="8"/>
+      <c r="AJ90" s="8"/>
+      <c r="AK90" s="8"/>
       <c r="AL90" s="2"/>
       <c r="AM90" s="2"/>
       <c r="AN90" s="2"/>
@@ -8911,8 +9250,11 @@
       <c r="CD90" s="2"/>
       <c r="CE90" s="2"/>
       <c r="CF90" s="2"/>
-    </row>
-    <row r="91" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG90" s="2"/>
+      <c r="CH90" s="2"/>
+      <c r="CI90" s="2"/>
+    </row>
+    <row r="91" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -8947,9 +9289,9 @@
       <c r="AF91" s="2"/>
       <c r="AG91" s="2"/>
       <c r="AH91" s="2"/>
-      <c r="AI91" s="2"/>
-      <c r="AJ91" s="2"/>
-      <c r="AK91" s="2"/>
+      <c r="AI91" s="8"/>
+      <c r="AJ91" s="8"/>
+      <c r="AK91" s="8"/>
       <c r="AL91" s="2"/>
       <c r="AM91" s="2"/>
       <c r="AN91" s="2"/>
@@ -8997,8 +9339,11 @@
       <c r="CD91" s="2"/>
       <c r="CE91" s="2"/>
       <c r="CF91" s="2"/>
-    </row>
-    <row r="92" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG91" s="2"/>
+      <c r="CH91" s="2"/>
+      <c r="CI91" s="2"/>
+    </row>
+    <row r="92" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -9033,9 +9378,9 @@
       <c r="AF92" s="2"/>
       <c r="AG92" s="2"/>
       <c r="AH92" s="2"/>
-      <c r="AI92" s="2"/>
-      <c r="AJ92" s="2"/>
-      <c r="AK92" s="2"/>
+      <c r="AI92" s="8"/>
+      <c r="AJ92" s="8"/>
+      <c r="AK92" s="8"/>
       <c r="AL92" s="2"/>
       <c r="AM92" s="2"/>
       <c r="AN92" s="2"/>
@@ -9083,8 +9428,11 @@
       <c r="CD92" s="2"/>
       <c r="CE92" s="2"/>
       <c r="CF92" s="2"/>
-    </row>
-    <row r="93" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG92" s="2"/>
+      <c r="CH92" s="2"/>
+      <c r="CI92" s="2"/>
+    </row>
+    <row r="93" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -9119,9 +9467,9 @@
       <c r="AF93" s="2"/>
       <c r="AG93" s="2"/>
       <c r="AH93" s="2"/>
-      <c r="AI93" s="2"/>
-      <c r="AJ93" s="2"/>
-      <c r="AK93" s="2"/>
+      <c r="AI93" s="8"/>
+      <c r="AJ93" s="8"/>
+      <c r="AK93" s="8"/>
       <c r="AL93" s="2"/>
       <c r="AM93" s="2"/>
       <c r="AN93" s="2"/>
@@ -9169,8 +9517,11 @@
       <c r="CD93" s="2"/>
       <c r="CE93" s="2"/>
       <c r="CF93" s="2"/>
-    </row>
-    <row r="94" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG93" s="2"/>
+      <c r="CH93" s="2"/>
+      <c r="CI93" s="2"/>
+    </row>
+    <row r="94" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -9205,9 +9556,9 @@
       <c r="AF94" s="2"/>
       <c r="AG94" s="2"/>
       <c r="AH94" s="2"/>
-      <c r="AI94" s="2"/>
-      <c r="AJ94" s="2"/>
-      <c r="AK94" s="2"/>
+      <c r="AI94" s="8"/>
+      <c r="AJ94" s="8"/>
+      <c r="AK94" s="8"/>
       <c r="AL94" s="2"/>
       <c r="AM94" s="2"/>
       <c r="AN94" s="2"/>
@@ -9255,8 +9606,11 @@
       <c r="CD94" s="2"/>
       <c r="CE94" s="2"/>
       <c r="CF94" s="2"/>
-    </row>
-    <row r="95" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG94" s="2"/>
+      <c r="CH94" s="2"/>
+      <c r="CI94" s="2"/>
+    </row>
+    <row r="95" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -9291,9 +9645,9 @@
       <c r="AF95" s="2"/>
       <c r="AG95" s="2"/>
       <c r="AH95" s="2"/>
-      <c r="AI95" s="2"/>
-      <c r="AJ95" s="2"/>
-      <c r="AK95" s="2"/>
+      <c r="AI95" s="8"/>
+      <c r="AJ95" s="8"/>
+      <c r="AK95" s="8"/>
       <c r="AL95" s="2"/>
       <c r="AM95" s="2"/>
       <c r="AN95" s="2"/>
@@ -9341,8 +9695,11 @@
       <c r="CD95" s="2"/>
       <c r="CE95" s="2"/>
       <c r="CF95" s="2"/>
-    </row>
-    <row r="96" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG95" s="2"/>
+      <c r="CH95" s="2"/>
+      <c r="CI95" s="2"/>
+    </row>
+    <row r="96" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -9377,9 +9734,9 @@
       <c r="AF96" s="2"/>
       <c r="AG96" s="2"/>
       <c r="AH96" s="2"/>
-      <c r="AI96" s="2"/>
-      <c r="AJ96" s="2"/>
-      <c r="AK96" s="2"/>
+      <c r="AI96" s="8"/>
+      <c r="AJ96" s="8"/>
+      <c r="AK96" s="8"/>
       <c r="AL96" s="2"/>
       <c r="AM96" s="2"/>
       <c r="AN96" s="2"/>
@@ -9427,8 +9784,11 @@
       <c r="CD96" s="2"/>
       <c r="CE96" s="2"/>
       <c r="CF96" s="2"/>
-    </row>
-    <row r="97" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG96" s="2"/>
+      <c r="CH96" s="2"/>
+      <c r="CI96" s="2"/>
+    </row>
+    <row r="97" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -9463,9 +9823,9 @@
       <c r="AF97" s="2"/>
       <c r="AG97" s="2"/>
       <c r="AH97" s="2"/>
-      <c r="AI97" s="2"/>
-      <c r="AJ97" s="2"/>
-      <c r="AK97" s="2"/>
+      <c r="AI97" s="8"/>
+      <c r="AJ97" s="8"/>
+      <c r="AK97" s="8"/>
       <c r="AL97" s="2"/>
       <c r="AM97" s="2"/>
       <c r="AN97" s="2"/>
@@ -9513,8 +9873,11 @@
       <c r="CD97" s="2"/>
       <c r="CE97" s="2"/>
       <c r="CF97" s="2"/>
-    </row>
-    <row r="98" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG97" s="2"/>
+      <c r="CH97" s="2"/>
+      <c r="CI97" s="2"/>
+    </row>
+    <row r="98" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -9549,9 +9912,9 @@
       <c r="AF98" s="2"/>
       <c r="AG98" s="2"/>
       <c r="AH98" s="2"/>
-      <c r="AI98" s="2"/>
-      <c r="AJ98" s="2"/>
-      <c r="AK98" s="2"/>
+      <c r="AI98" s="8"/>
+      <c r="AJ98" s="8"/>
+      <c r="AK98" s="8"/>
       <c r="AL98" s="2"/>
       <c r="AM98" s="2"/>
       <c r="AN98" s="2"/>
@@ -9599,8 +9962,11 @@
       <c r="CD98" s="2"/>
       <c r="CE98" s="2"/>
       <c r="CF98" s="2"/>
-    </row>
-    <row r="99" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG98" s="2"/>
+      <c r="CH98" s="2"/>
+      <c r="CI98" s="2"/>
+    </row>
+    <row r="99" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -9635,9 +10001,9 @@
       <c r="AF99" s="2"/>
       <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
-      <c r="AI99" s="2"/>
-      <c r="AJ99" s="2"/>
-      <c r="AK99" s="2"/>
+      <c r="AI99" s="8"/>
+      <c r="AJ99" s="8"/>
+      <c r="AK99" s="8"/>
       <c r="AL99" s="2"/>
       <c r="AM99" s="2"/>
       <c r="AN99" s="2"/>
@@ -9685,8 +10051,11 @@
       <c r="CD99" s="2"/>
       <c r="CE99" s="2"/>
       <c r="CF99" s="2"/>
-    </row>
-    <row r="100" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG99" s="2"/>
+      <c r="CH99" s="2"/>
+      <c r="CI99" s="2"/>
+    </row>
+    <row r="100" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -9721,9 +10090,9 @@
       <c r="AF100" s="2"/>
       <c r="AG100" s="2"/>
       <c r="AH100" s="2"/>
-      <c r="AI100" s="2"/>
-      <c r="AJ100" s="2"/>
-      <c r="AK100" s="2"/>
+      <c r="AI100" s="8"/>
+      <c r="AJ100" s="8"/>
+      <c r="AK100" s="8"/>
       <c r="AL100" s="2"/>
       <c r="AM100" s="2"/>
       <c r="AN100" s="2"/>
@@ -9771,8 +10140,11 @@
       <c r="CD100" s="2"/>
       <c r="CE100" s="2"/>
       <c r="CF100" s="2"/>
-    </row>
-    <row r="101" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG100" s="2"/>
+      <c r="CH100" s="2"/>
+      <c r="CI100" s="2"/>
+    </row>
+    <row r="101" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -9807,9 +10179,9 @@
       <c r="AF101" s="2"/>
       <c r="AG101" s="2"/>
       <c r="AH101" s="2"/>
-      <c r="AI101" s="2"/>
-      <c r="AJ101" s="2"/>
-      <c r="AK101" s="2"/>
+      <c r="AI101" s="8"/>
+      <c r="AJ101" s="8"/>
+      <c r="AK101" s="8"/>
       <c r="AL101" s="2"/>
       <c r="AM101" s="2"/>
       <c r="AN101" s="2"/>
@@ -9857,8 +10229,11 @@
       <c r="CD101" s="2"/>
       <c r="CE101" s="2"/>
       <c r="CF101" s="2"/>
-    </row>
-    <row r="102" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG101" s="2"/>
+      <c r="CH101" s="2"/>
+      <c r="CI101" s="2"/>
+    </row>
+    <row r="102" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -9893,9 +10268,9 @@
       <c r="AF102" s="2"/>
       <c r="AG102" s="2"/>
       <c r="AH102" s="2"/>
-      <c r="AI102" s="2"/>
-      <c r="AJ102" s="2"/>
-      <c r="AK102" s="2"/>
+      <c r="AI102" s="8"/>
+      <c r="AJ102" s="8"/>
+      <c r="AK102" s="8"/>
       <c r="AL102" s="2"/>
       <c r="AM102" s="2"/>
       <c r="AN102" s="2"/>
@@ -9943,8 +10318,11 @@
       <c r="CD102" s="2"/>
       <c r="CE102" s="2"/>
       <c r="CF102" s="2"/>
-    </row>
-    <row r="103" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG102" s="2"/>
+      <c r="CH102" s="2"/>
+      <c r="CI102" s="2"/>
+    </row>
+    <row r="103" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -9979,9 +10357,9 @@
       <c r="AF103" s="2"/>
       <c r="AG103" s="2"/>
       <c r="AH103" s="2"/>
-      <c r="AI103" s="2"/>
-      <c r="AJ103" s="2"/>
-      <c r="AK103" s="2"/>
+      <c r="AI103" s="8"/>
+      <c r="AJ103" s="8"/>
+      <c r="AK103" s="8"/>
       <c r="AL103" s="2"/>
       <c r="AM103" s="2"/>
       <c r="AN103" s="2"/>
@@ -10029,8 +10407,11 @@
       <c r="CD103" s="2"/>
       <c r="CE103" s="2"/>
       <c r="CF103" s="2"/>
-    </row>
-    <row r="104" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG103" s="2"/>
+      <c r="CH103" s="2"/>
+      <c r="CI103" s="2"/>
+    </row>
+    <row r="104" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -10065,9 +10446,9 @@
       <c r="AF104" s="2"/>
       <c r="AG104" s="2"/>
       <c r="AH104" s="2"/>
-      <c r="AI104" s="2"/>
-      <c r="AJ104" s="2"/>
-      <c r="AK104" s="2"/>
+      <c r="AI104" s="8"/>
+      <c r="AJ104" s="8"/>
+      <c r="AK104" s="8"/>
       <c r="AL104" s="2"/>
       <c r="AM104" s="2"/>
       <c r="AN104" s="2"/>
@@ -10115,8 +10496,11 @@
       <c r="CD104" s="2"/>
       <c r="CE104" s="2"/>
       <c r="CF104" s="2"/>
-    </row>
-    <row r="105" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG104" s="2"/>
+      <c r="CH104" s="2"/>
+      <c r="CI104" s="2"/>
+    </row>
+    <row r="105" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -10151,9 +10535,9 @@
       <c r="AF105" s="2"/>
       <c r="AG105" s="2"/>
       <c r="AH105" s="2"/>
-      <c r="AI105" s="2"/>
-      <c r="AJ105" s="2"/>
-      <c r="AK105" s="2"/>
+      <c r="AI105" s="8"/>
+      <c r="AJ105" s="8"/>
+      <c r="AK105" s="8"/>
       <c r="AL105" s="2"/>
       <c r="AM105" s="2"/>
       <c r="AN105" s="2"/>
@@ -10201,8 +10585,11 @@
       <c r="CD105" s="2"/>
       <c r="CE105" s="2"/>
       <c r="CF105" s="2"/>
-    </row>
-    <row r="106" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG105" s="2"/>
+      <c r="CH105" s="2"/>
+      <c r="CI105" s="2"/>
+    </row>
+    <row r="106" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -10237,9 +10624,9 @@
       <c r="AF106" s="2"/>
       <c r="AG106" s="2"/>
       <c r="AH106" s="2"/>
-      <c r="AI106" s="2"/>
-      <c r="AJ106" s="2"/>
-      <c r="AK106" s="2"/>
+      <c r="AI106" s="8"/>
+      <c r="AJ106" s="8"/>
+      <c r="AK106" s="8"/>
       <c r="AL106" s="2"/>
       <c r="AM106" s="2"/>
       <c r="AN106" s="2"/>
@@ -10287,8 +10674,11 @@
       <c r="CD106" s="2"/>
       <c r="CE106" s="2"/>
       <c r="CF106" s="2"/>
-    </row>
-    <row r="107" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG106" s="2"/>
+      <c r="CH106" s="2"/>
+      <c r="CI106" s="2"/>
+    </row>
+    <row r="107" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -10323,9 +10713,9 @@
       <c r="AF107" s="2"/>
       <c r="AG107" s="2"/>
       <c r="AH107" s="2"/>
-      <c r="AI107" s="2"/>
-      <c r="AJ107" s="2"/>
-      <c r="AK107" s="2"/>
+      <c r="AI107" s="8"/>
+      <c r="AJ107" s="8"/>
+      <c r="AK107" s="8"/>
       <c r="AL107" s="2"/>
       <c r="AM107" s="2"/>
       <c r="AN107" s="2"/>
@@ -10373,8 +10763,11 @@
       <c r="CD107" s="2"/>
       <c r="CE107" s="2"/>
       <c r="CF107" s="2"/>
-    </row>
-    <row r="108" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG107" s="2"/>
+      <c r="CH107" s="2"/>
+      <c r="CI107" s="2"/>
+    </row>
+    <row r="108" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -10409,9 +10802,9 @@
       <c r="AF108" s="2"/>
       <c r="AG108" s="2"/>
       <c r="AH108" s="2"/>
-      <c r="AI108" s="2"/>
-      <c r="AJ108" s="2"/>
-      <c r="AK108" s="2"/>
+      <c r="AI108" s="8"/>
+      <c r="AJ108" s="8"/>
+      <c r="AK108" s="8"/>
       <c r="AL108" s="2"/>
       <c r="AM108" s="2"/>
       <c r="AN108" s="2"/>
@@ -10459,8 +10852,11 @@
       <c r="CD108" s="2"/>
       <c r="CE108" s="2"/>
       <c r="CF108" s="2"/>
-    </row>
-    <row r="109" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG108" s="2"/>
+      <c r="CH108" s="2"/>
+      <c r="CI108" s="2"/>
+    </row>
+    <row r="109" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -10495,9 +10891,9 @@
       <c r="AF109" s="2"/>
       <c r="AG109" s="2"/>
       <c r="AH109" s="2"/>
-      <c r="AI109" s="2"/>
-      <c r="AJ109" s="2"/>
-      <c r="AK109" s="2"/>
+      <c r="AI109" s="8"/>
+      <c r="AJ109" s="8"/>
+      <c r="AK109" s="8"/>
       <c r="AL109" s="2"/>
       <c r="AM109" s="2"/>
       <c r="AN109" s="2"/>
@@ -10545,8 +10941,11 @@
       <c r="CD109" s="2"/>
       <c r="CE109" s="2"/>
       <c r="CF109" s="2"/>
-    </row>
-    <row r="110" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG109" s="2"/>
+      <c r="CH109" s="2"/>
+      <c r="CI109" s="2"/>
+    </row>
+    <row r="110" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -10581,9 +10980,9 @@
       <c r="AF110" s="2"/>
       <c r="AG110" s="2"/>
       <c r="AH110" s="2"/>
-      <c r="AI110" s="2"/>
-      <c r="AJ110" s="2"/>
-      <c r="AK110" s="2"/>
+      <c r="AI110" s="8"/>
+      <c r="AJ110" s="8"/>
+      <c r="AK110" s="8"/>
       <c r="AL110" s="2"/>
       <c r="AM110" s="2"/>
       <c r="AN110" s="2"/>
@@ -10631,8 +11030,11 @@
       <c r="CD110" s="2"/>
       <c r="CE110" s="2"/>
       <c r="CF110" s="2"/>
-    </row>
-    <row r="111" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG110" s="2"/>
+      <c r="CH110" s="2"/>
+      <c r="CI110" s="2"/>
+    </row>
+    <row r="111" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -10667,9 +11069,9 @@
       <c r="AF111" s="2"/>
       <c r="AG111" s="2"/>
       <c r="AH111" s="2"/>
-      <c r="AI111" s="2"/>
-      <c r="AJ111" s="2"/>
-      <c r="AK111" s="2"/>
+      <c r="AI111" s="8"/>
+      <c r="AJ111" s="8"/>
+      <c r="AK111" s="8"/>
       <c r="AL111" s="2"/>
       <c r="AM111" s="2"/>
       <c r="AN111" s="2"/>
@@ -10717,8 +11119,11 @@
       <c r="CD111" s="2"/>
       <c r="CE111" s="2"/>
       <c r="CF111" s="2"/>
-    </row>
-    <row r="112" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG111" s="2"/>
+      <c r="CH111" s="2"/>
+      <c r="CI111" s="2"/>
+    </row>
+    <row r="112" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -10753,9 +11158,9 @@
       <c r="AF112" s="2"/>
       <c r="AG112" s="2"/>
       <c r="AH112" s="2"/>
-      <c r="AI112" s="2"/>
-      <c r="AJ112" s="2"/>
-      <c r="AK112" s="2"/>
+      <c r="AI112" s="8"/>
+      <c r="AJ112" s="8"/>
+      <c r="AK112" s="8"/>
       <c r="AL112" s="2"/>
       <c r="AM112" s="2"/>
       <c r="AN112" s="2"/>
@@ -10803,8 +11208,11 @@
       <c r="CD112" s="2"/>
       <c r="CE112" s="2"/>
       <c r="CF112" s="2"/>
-    </row>
-    <row r="113" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG112" s="2"/>
+      <c r="CH112" s="2"/>
+      <c r="CI112" s="2"/>
+    </row>
+    <row r="113" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -10839,9 +11247,9 @@
       <c r="AF113" s="2"/>
       <c r="AG113" s="2"/>
       <c r="AH113" s="2"/>
-      <c r="AI113" s="2"/>
-      <c r="AJ113" s="2"/>
-      <c r="AK113" s="2"/>
+      <c r="AI113" s="8"/>
+      <c r="AJ113" s="8"/>
+      <c r="AK113" s="8"/>
       <c r="AL113" s="2"/>
       <c r="AM113" s="2"/>
       <c r="AN113" s="2"/>
@@ -10889,8 +11297,11 @@
       <c r="CD113" s="2"/>
       <c r="CE113" s="2"/>
       <c r="CF113" s="2"/>
-    </row>
-    <row r="114" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG113" s="2"/>
+      <c r="CH113" s="2"/>
+      <c r="CI113" s="2"/>
+    </row>
+    <row r="114" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -10925,9 +11336,9 @@
       <c r="AF114" s="2"/>
       <c r="AG114" s="2"/>
       <c r="AH114" s="2"/>
-      <c r="AI114" s="2"/>
-      <c r="AJ114" s="2"/>
-      <c r="AK114" s="2"/>
+      <c r="AI114" s="8"/>
+      <c r="AJ114" s="8"/>
+      <c r="AK114" s="8"/>
       <c r="AL114" s="2"/>
       <c r="AM114" s="2"/>
       <c r="AN114" s="2"/>
@@ -10975,8 +11386,11 @@
       <c r="CD114" s="2"/>
       <c r="CE114" s="2"/>
       <c r="CF114" s="2"/>
-    </row>
-    <row r="115" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG114" s="2"/>
+      <c r="CH114" s="2"/>
+      <c r="CI114" s="2"/>
+    </row>
+    <row r="115" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -11011,9 +11425,9 @@
       <c r="AF115" s="2"/>
       <c r="AG115" s="2"/>
       <c r="AH115" s="2"/>
-      <c r="AI115" s="2"/>
-      <c r="AJ115" s="2"/>
-      <c r="AK115" s="2"/>
+      <c r="AI115" s="8"/>
+      <c r="AJ115" s="8"/>
+      <c r="AK115" s="8"/>
       <c r="AL115" s="2"/>
       <c r="AM115" s="2"/>
       <c r="AN115" s="2"/>
@@ -11061,8 +11475,11 @@
       <c r="CD115" s="2"/>
       <c r="CE115" s="2"/>
       <c r="CF115" s="2"/>
-    </row>
-    <row r="116" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG115" s="2"/>
+      <c r="CH115" s="2"/>
+      <c r="CI115" s="2"/>
+    </row>
+    <row r="116" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -11097,9 +11514,9 @@
       <c r="AF116" s="2"/>
       <c r="AG116" s="2"/>
       <c r="AH116" s="2"/>
-      <c r="AI116" s="2"/>
-      <c r="AJ116" s="2"/>
-      <c r="AK116" s="2"/>
+      <c r="AI116" s="8"/>
+      <c r="AJ116" s="8"/>
+      <c r="AK116" s="8"/>
       <c r="AL116" s="2"/>
       <c r="AM116" s="2"/>
       <c r="AN116" s="2"/>
@@ -11147,8 +11564,11 @@
       <c r="CD116" s="2"/>
       <c r="CE116" s="2"/>
       <c r="CF116" s="2"/>
-    </row>
-    <row r="117" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG116" s="2"/>
+      <c r="CH116" s="2"/>
+      <c r="CI116" s="2"/>
+    </row>
+    <row r="117" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -11183,9 +11603,9 @@
       <c r="AF117" s="2"/>
       <c r="AG117" s="2"/>
       <c r="AH117" s="2"/>
-      <c r="AI117" s="2"/>
-      <c r="AJ117" s="2"/>
-      <c r="AK117" s="2"/>
+      <c r="AI117" s="8"/>
+      <c r="AJ117" s="8"/>
+      <c r="AK117" s="8"/>
       <c r="AL117" s="2"/>
       <c r="AM117" s="2"/>
       <c r="AN117" s="2"/>
@@ -11233,8 +11653,11 @@
       <c r="CD117" s="2"/>
       <c r="CE117" s="2"/>
       <c r="CF117" s="2"/>
-    </row>
-    <row r="118" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG117" s="2"/>
+      <c r="CH117" s="2"/>
+      <c r="CI117" s="2"/>
+    </row>
+    <row r="118" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -11269,9 +11692,9 @@
       <c r="AF118" s="2"/>
       <c r="AG118" s="2"/>
       <c r="AH118" s="2"/>
-      <c r="AI118" s="2"/>
-      <c r="AJ118" s="2"/>
-      <c r="AK118" s="2"/>
+      <c r="AI118" s="8"/>
+      <c r="AJ118" s="8"/>
+      <c r="AK118" s="8"/>
       <c r="AL118" s="2"/>
       <c r="AM118" s="2"/>
       <c r="AN118" s="2"/>
@@ -11319,8 +11742,11 @@
       <c r="CD118" s="2"/>
       <c r="CE118" s="2"/>
       <c r="CF118" s="2"/>
-    </row>
-    <row r="119" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG118" s="2"/>
+      <c r="CH118" s="2"/>
+      <c r="CI118" s="2"/>
+    </row>
+    <row r="119" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -11355,9 +11781,9 @@
       <c r="AF119" s="2"/>
       <c r="AG119" s="2"/>
       <c r="AH119" s="2"/>
-      <c r="AI119" s="2"/>
-      <c r="AJ119" s="2"/>
-      <c r="AK119" s="2"/>
+      <c r="AI119" s="8"/>
+      <c r="AJ119" s="8"/>
+      <c r="AK119" s="8"/>
       <c r="AL119" s="2"/>
       <c r="AM119" s="2"/>
       <c r="AN119" s="2"/>
@@ -11405,8 +11831,11 @@
       <c r="CD119" s="2"/>
       <c r="CE119" s="2"/>
       <c r="CF119" s="2"/>
-    </row>
-    <row r="120" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG119" s="2"/>
+      <c r="CH119" s="2"/>
+      <c r="CI119" s="2"/>
+    </row>
+    <row r="120" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -11441,9 +11870,9 @@
       <c r="AF120" s="2"/>
       <c r="AG120" s="2"/>
       <c r="AH120" s="2"/>
-      <c r="AI120" s="2"/>
-      <c r="AJ120" s="2"/>
-      <c r="AK120" s="2"/>
+      <c r="AI120" s="8"/>
+      <c r="AJ120" s="8"/>
+      <c r="AK120" s="8"/>
       <c r="AL120" s="2"/>
       <c r="AM120" s="2"/>
       <c r="AN120" s="2"/>
@@ -11491,8 +11920,11 @@
       <c r="CD120" s="2"/>
       <c r="CE120" s="2"/>
       <c r="CF120" s="2"/>
-    </row>
-    <row r="121" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG120" s="2"/>
+      <c r="CH120" s="2"/>
+      <c r="CI120" s="2"/>
+    </row>
+    <row r="121" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -11527,9 +11959,9 @@
       <c r="AF121" s="2"/>
       <c r="AG121" s="2"/>
       <c r="AH121" s="2"/>
-      <c r="AI121" s="2"/>
-      <c r="AJ121" s="2"/>
-      <c r="AK121" s="2"/>
+      <c r="AI121" s="8"/>
+      <c r="AJ121" s="8"/>
+      <c r="AK121" s="8"/>
       <c r="AL121" s="2"/>
       <c r="AM121" s="2"/>
       <c r="AN121" s="2"/>
@@ -11577,8 +12009,11 @@
       <c r="CD121" s="2"/>
       <c r="CE121" s="2"/>
       <c r="CF121" s="2"/>
-    </row>
-    <row r="122" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG121" s="2"/>
+      <c r="CH121" s="2"/>
+      <c r="CI121" s="2"/>
+    </row>
+    <row r="122" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -11613,9 +12048,9 @@
       <c r="AF122" s="2"/>
       <c r="AG122" s="2"/>
       <c r="AH122" s="2"/>
-      <c r="AI122" s="2"/>
-      <c r="AJ122" s="2"/>
-      <c r="AK122" s="2"/>
+      <c r="AI122" s="8"/>
+      <c r="AJ122" s="8"/>
+      <c r="AK122" s="8"/>
       <c r="AL122" s="2"/>
       <c r="AM122" s="2"/>
       <c r="AN122" s="2"/>
@@ -11663,8 +12098,11 @@
       <c r="CD122" s="2"/>
       <c r="CE122" s="2"/>
       <c r="CF122" s="2"/>
-    </row>
-    <row r="123" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG122" s="2"/>
+      <c r="CH122" s="2"/>
+      <c r="CI122" s="2"/>
+    </row>
+    <row r="123" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -11699,9 +12137,9 @@
       <c r="AF123" s="2"/>
       <c r="AG123" s="2"/>
       <c r="AH123" s="2"/>
-      <c r="AI123" s="2"/>
-      <c r="AJ123" s="2"/>
-      <c r="AK123" s="2"/>
+      <c r="AI123" s="8"/>
+      <c r="AJ123" s="8"/>
+      <c r="AK123" s="8"/>
       <c r="AL123" s="2"/>
       <c r="AM123" s="2"/>
       <c r="AN123" s="2"/>
@@ -11749,8 +12187,11 @@
       <c r="CD123" s="2"/>
       <c r="CE123" s="2"/>
       <c r="CF123" s="2"/>
-    </row>
-    <row r="124" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG123" s="2"/>
+      <c r="CH123" s="2"/>
+      <c r="CI123" s="2"/>
+    </row>
+    <row r="124" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -11785,9 +12226,9 @@
       <c r="AF124" s="2"/>
       <c r="AG124" s="2"/>
       <c r="AH124" s="2"/>
-      <c r="AI124" s="2"/>
-      <c r="AJ124" s="2"/>
-      <c r="AK124" s="2"/>
+      <c r="AI124" s="8"/>
+      <c r="AJ124" s="8"/>
+      <c r="AK124" s="8"/>
       <c r="AL124" s="2"/>
       <c r="AM124" s="2"/>
       <c r="AN124" s="2"/>
@@ -11835,8 +12276,11 @@
       <c r="CD124" s="2"/>
       <c r="CE124" s="2"/>
       <c r="CF124" s="2"/>
-    </row>
-    <row r="125" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG124" s="2"/>
+      <c r="CH124" s="2"/>
+      <c r="CI124" s="2"/>
+    </row>
+    <row r="125" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -11871,9 +12315,9 @@
       <c r="AF125" s="2"/>
       <c r="AG125" s="2"/>
       <c r="AH125" s="2"/>
-      <c r="AI125" s="2"/>
-      <c r="AJ125" s="2"/>
-      <c r="AK125" s="2"/>
+      <c r="AI125" s="8"/>
+      <c r="AJ125" s="8"/>
+      <c r="AK125" s="8"/>
       <c r="AL125" s="2"/>
       <c r="AM125" s="2"/>
       <c r="AN125" s="2"/>
@@ -11921,8 +12365,11 @@
       <c r="CD125" s="2"/>
       <c r="CE125" s="2"/>
       <c r="CF125" s="2"/>
-    </row>
-    <row r="126" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG125" s="2"/>
+      <c r="CH125" s="2"/>
+      <c r="CI125" s="2"/>
+    </row>
+    <row r="126" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -11957,9 +12404,9 @@
       <c r="AF126" s="2"/>
       <c r="AG126" s="2"/>
       <c r="AH126" s="2"/>
-      <c r="AI126" s="2"/>
-      <c r="AJ126" s="2"/>
-      <c r="AK126" s="2"/>
+      <c r="AI126" s="8"/>
+      <c r="AJ126" s="8"/>
+      <c r="AK126" s="8"/>
       <c r="AL126" s="2"/>
       <c r="AM126" s="2"/>
       <c r="AN126" s="2"/>
@@ -12007,8 +12454,11 @@
       <c r="CD126" s="2"/>
       <c r="CE126" s="2"/>
       <c r="CF126" s="2"/>
-    </row>
-    <row r="127" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG126" s="2"/>
+      <c r="CH126" s="2"/>
+      <c r="CI126" s="2"/>
+    </row>
+    <row r="127" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -12043,9 +12493,9 @@
       <c r="AF127" s="2"/>
       <c r="AG127" s="2"/>
       <c r="AH127" s="2"/>
-      <c r="AI127" s="2"/>
-      <c r="AJ127" s="2"/>
-      <c r="AK127" s="2"/>
+      <c r="AI127" s="8"/>
+      <c r="AJ127" s="8"/>
+      <c r="AK127" s="8"/>
       <c r="AL127" s="2"/>
       <c r="AM127" s="2"/>
       <c r="AN127" s="2"/>
@@ -12093,8 +12543,11 @@
       <c r="CD127" s="2"/>
       <c r="CE127" s="2"/>
       <c r="CF127" s="2"/>
-    </row>
-    <row r="128" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG127" s="2"/>
+      <c r="CH127" s="2"/>
+      <c r="CI127" s="2"/>
+    </row>
+    <row r="128" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -12129,9 +12582,9 @@
       <c r="AF128" s="2"/>
       <c r="AG128" s="2"/>
       <c r="AH128" s="2"/>
-      <c r="AI128" s="2"/>
-      <c r="AJ128" s="2"/>
-      <c r="AK128" s="2"/>
+      <c r="AI128" s="8"/>
+      <c r="AJ128" s="8"/>
+      <c r="AK128" s="8"/>
       <c r="AL128" s="2"/>
       <c r="AM128" s="2"/>
       <c r="AN128" s="2"/>
@@ -12179,8 +12632,11 @@
       <c r="CD128" s="2"/>
       <c r="CE128" s="2"/>
       <c r="CF128" s="2"/>
-    </row>
-    <row r="129" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG128" s="2"/>
+      <c r="CH128" s="2"/>
+      <c r="CI128" s="2"/>
+    </row>
+    <row r="129" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -12215,9 +12671,9 @@
       <c r="AF129" s="2"/>
       <c r="AG129" s="2"/>
       <c r="AH129" s="2"/>
-      <c r="AI129" s="2"/>
-      <c r="AJ129" s="2"/>
-      <c r="AK129" s="2"/>
+      <c r="AI129" s="8"/>
+      <c r="AJ129" s="8"/>
+      <c r="AK129" s="8"/>
       <c r="AL129" s="2"/>
       <c r="AM129" s="2"/>
       <c r="AN129" s="2"/>
@@ -12265,8 +12721,11 @@
       <c r="CD129" s="2"/>
       <c r="CE129" s="2"/>
       <c r="CF129" s="2"/>
-    </row>
-    <row r="130" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG129" s="2"/>
+      <c r="CH129" s="2"/>
+      <c r="CI129" s="2"/>
+    </row>
+    <row r="130" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -12301,9 +12760,9 @@
       <c r="AF130" s="2"/>
       <c r="AG130" s="2"/>
       <c r="AH130" s="2"/>
-      <c r="AI130" s="2"/>
-      <c r="AJ130" s="2"/>
-      <c r="AK130" s="2"/>
+      <c r="AI130" s="8"/>
+      <c r="AJ130" s="8"/>
+      <c r="AK130" s="8"/>
       <c r="AL130" s="2"/>
       <c r="AM130" s="2"/>
       <c r="AN130" s="2"/>
@@ -12351,8 +12810,11 @@
       <c r="CD130" s="2"/>
       <c r="CE130" s="2"/>
       <c r="CF130" s="2"/>
-    </row>
-    <row r="131" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG130" s="2"/>
+      <c r="CH130" s="2"/>
+      <c r="CI130" s="2"/>
+    </row>
+    <row r="131" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -12387,9 +12849,9 @@
       <c r="AF131" s="2"/>
       <c r="AG131" s="2"/>
       <c r="AH131" s="2"/>
-      <c r="AI131" s="2"/>
-      <c r="AJ131" s="2"/>
-      <c r="AK131" s="2"/>
+      <c r="AI131" s="8"/>
+      <c r="AJ131" s="8"/>
+      <c r="AK131" s="8"/>
       <c r="AL131" s="2"/>
       <c r="AM131" s="2"/>
       <c r="AN131" s="2"/>
@@ -12437,8 +12899,11 @@
       <c r="CD131" s="2"/>
       <c r="CE131" s="2"/>
       <c r="CF131" s="2"/>
-    </row>
-    <row r="132" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG131" s="2"/>
+      <c r="CH131" s="2"/>
+      <c r="CI131" s="2"/>
+    </row>
+    <row r="132" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -12473,9 +12938,9 @@
       <c r="AF132" s="2"/>
       <c r="AG132" s="2"/>
       <c r="AH132" s="2"/>
-      <c r="AI132" s="2"/>
-      <c r="AJ132" s="2"/>
-      <c r="AK132" s="2"/>
+      <c r="AI132" s="8"/>
+      <c r="AJ132" s="8"/>
+      <c r="AK132" s="8"/>
       <c r="AL132" s="2"/>
       <c r="AM132" s="2"/>
       <c r="AN132" s="2"/>
@@ -12523,8 +12988,11 @@
       <c r="CD132" s="2"/>
       <c r="CE132" s="2"/>
       <c r="CF132" s="2"/>
-    </row>
-    <row r="133" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG132" s="2"/>
+      <c r="CH132" s="2"/>
+      <c r="CI132" s="2"/>
+    </row>
+    <row r="133" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -12559,9 +13027,9 @@
       <c r="AF133" s="2"/>
       <c r="AG133" s="2"/>
       <c r="AH133" s="2"/>
-      <c r="AI133" s="2"/>
-      <c r="AJ133" s="2"/>
-      <c r="AK133" s="2"/>
+      <c r="AI133" s="8"/>
+      <c r="AJ133" s="8"/>
+      <c r="AK133" s="8"/>
       <c r="AL133" s="2"/>
       <c r="AM133" s="2"/>
       <c r="AN133" s="2"/>
@@ -12609,8 +13077,11 @@
       <c r="CD133" s="2"/>
       <c r="CE133" s="2"/>
       <c r="CF133" s="2"/>
-    </row>
-    <row r="134" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG133" s="2"/>
+      <c r="CH133" s="2"/>
+      <c r="CI133" s="2"/>
+    </row>
+    <row r="134" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -12645,9 +13116,9 @@
       <c r="AF134" s="2"/>
       <c r="AG134" s="2"/>
       <c r="AH134" s="2"/>
-      <c r="AI134" s="2"/>
-      <c r="AJ134" s="2"/>
-      <c r="AK134" s="2"/>
+      <c r="AI134" s="8"/>
+      <c r="AJ134" s="8"/>
+      <c r="AK134" s="8"/>
       <c r="AL134" s="2"/>
       <c r="AM134" s="2"/>
       <c r="AN134" s="2"/>
@@ -12695,8 +13166,11 @@
       <c r="CD134" s="2"/>
       <c r="CE134" s="2"/>
       <c r="CF134" s="2"/>
-    </row>
-    <row r="135" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG134" s="2"/>
+      <c r="CH134" s="2"/>
+      <c r="CI134" s="2"/>
+    </row>
+    <row r="135" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -12731,9 +13205,9 @@
       <c r="AF135" s="2"/>
       <c r="AG135" s="2"/>
       <c r="AH135" s="2"/>
-      <c r="AI135" s="2"/>
-      <c r="AJ135" s="2"/>
-      <c r="AK135" s="2"/>
+      <c r="AI135" s="8"/>
+      <c r="AJ135" s="8"/>
+      <c r="AK135" s="8"/>
       <c r="AL135" s="2"/>
       <c r="AM135" s="2"/>
       <c r="AN135" s="2"/>
@@ -12781,8 +13255,11 @@
       <c r="CD135" s="2"/>
       <c r="CE135" s="2"/>
       <c r="CF135" s="2"/>
-    </row>
-    <row r="136" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG135" s="2"/>
+      <c r="CH135" s="2"/>
+      <c r="CI135" s="2"/>
+    </row>
+    <row r="136" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -12817,9 +13294,9 @@
       <c r="AF136" s="2"/>
       <c r="AG136" s="2"/>
       <c r="AH136" s="2"/>
-      <c r="AI136" s="2"/>
-      <c r="AJ136" s="2"/>
-      <c r="AK136" s="2"/>
+      <c r="AI136" s="8"/>
+      <c r="AJ136" s="8"/>
+      <c r="AK136" s="8"/>
       <c r="AL136" s="2"/>
       <c r="AM136" s="2"/>
       <c r="AN136" s="2"/>
@@ -12867,8 +13344,11 @@
       <c r="CD136" s="2"/>
       <c r="CE136" s="2"/>
       <c r="CF136" s="2"/>
-    </row>
-    <row r="137" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG136" s="2"/>
+      <c r="CH136" s="2"/>
+      <c r="CI136" s="2"/>
+    </row>
+    <row r="137" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -12903,9 +13383,9 @@
       <c r="AF137" s="2"/>
       <c r="AG137" s="2"/>
       <c r="AH137" s="2"/>
-      <c r="AI137" s="2"/>
-      <c r="AJ137" s="2"/>
-      <c r="AK137" s="2"/>
+      <c r="AI137" s="8"/>
+      <c r="AJ137" s="8"/>
+      <c r="AK137" s="8"/>
       <c r="AL137" s="2"/>
       <c r="AM137" s="2"/>
       <c r="AN137" s="2"/>
@@ -12953,8 +13433,11 @@
       <c r="CD137" s="2"/>
       <c r="CE137" s="2"/>
       <c r="CF137" s="2"/>
-    </row>
-    <row r="138" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG137" s="2"/>
+      <c r="CH137" s="2"/>
+      <c r="CI137" s="2"/>
+    </row>
+    <row r="138" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -12989,9 +13472,9 @@
       <c r="AF138" s="2"/>
       <c r="AG138" s="2"/>
       <c r="AH138" s="2"/>
-      <c r="AI138" s="2"/>
-      <c r="AJ138" s="2"/>
-      <c r="AK138" s="2"/>
+      <c r="AI138" s="8"/>
+      <c r="AJ138" s="8"/>
+      <c r="AK138" s="8"/>
       <c r="AL138" s="2"/>
       <c r="AM138" s="2"/>
       <c r="AN138" s="2"/>
@@ -13039,8 +13522,11 @@
       <c r="CD138" s="2"/>
       <c r="CE138" s="2"/>
       <c r="CF138" s="2"/>
-    </row>
-    <row r="139" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG138" s="2"/>
+      <c r="CH138" s="2"/>
+      <c r="CI138" s="2"/>
+    </row>
+    <row r="139" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -13075,9 +13561,9 @@
       <c r="AF139" s="2"/>
       <c r="AG139" s="2"/>
       <c r="AH139" s="2"/>
-      <c r="AI139" s="2"/>
-      <c r="AJ139" s="2"/>
-      <c r="AK139" s="2"/>
+      <c r="AI139" s="8"/>
+      <c r="AJ139" s="8"/>
+      <c r="AK139" s="8"/>
       <c r="AL139" s="2"/>
       <c r="AM139" s="2"/>
       <c r="AN139" s="2"/>
@@ -13125,8 +13611,11 @@
       <c r="CD139" s="2"/>
       <c r="CE139" s="2"/>
       <c r="CF139" s="2"/>
-    </row>
-    <row r="140" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG139" s="2"/>
+      <c r="CH139" s="2"/>
+      <c r="CI139" s="2"/>
+    </row>
+    <row r="140" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -13161,9 +13650,9 @@
       <c r="AF140" s="2"/>
       <c r="AG140" s="2"/>
       <c r="AH140" s="2"/>
-      <c r="AI140" s="2"/>
-      <c r="AJ140" s="2"/>
-      <c r="AK140" s="2"/>
+      <c r="AI140" s="8"/>
+      <c r="AJ140" s="8"/>
+      <c r="AK140" s="8"/>
       <c r="AL140" s="2"/>
       <c r="AM140" s="2"/>
       <c r="AN140" s="2"/>
@@ -13211,8 +13700,11 @@
       <c r="CD140" s="2"/>
       <c r="CE140" s="2"/>
       <c r="CF140" s="2"/>
-    </row>
-    <row r="141" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG140" s="2"/>
+      <c r="CH140" s="2"/>
+      <c r="CI140" s="2"/>
+    </row>
+    <row r="141" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -13247,9 +13739,9 @@
       <c r="AF141" s="2"/>
       <c r="AG141" s="2"/>
       <c r="AH141" s="2"/>
-      <c r="AI141" s="2"/>
-      <c r="AJ141" s="2"/>
-      <c r="AK141" s="2"/>
+      <c r="AI141" s="8"/>
+      <c r="AJ141" s="8"/>
+      <c r="AK141" s="8"/>
       <c r="AL141" s="2"/>
       <c r="AM141" s="2"/>
       <c r="AN141" s="2"/>
@@ -13297,8 +13789,11 @@
       <c r="CD141" s="2"/>
       <c r="CE141" s="2"/>
       <c r="CF141" s="2"/>
-    </row>
-    <row r="142" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG141" s="2"/>
+      <c r="CH141" s="2"/>
+      <c r="CI141" s="2"/>
+    </row>
+    <row r="142" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -13333,9 +13828,9 @@
       <c r="AF142" s="2"/>
       <c r="AG142" s="2"/>
       <c r="AH142" s="2"/>
-      <c r="AI142" s="2"/>
-      <c r="AJ142" s="2"/>
-      <c r="AK142" s="2"/>
+      <c r="AI142" s="8"/>
+      <c r="AJ142" s="8"/>
+      <c r="AK142" s="8"/>
       <c r="AL142" s="2"/>
       <c r="AM142" s="2"/>
       <c r="AN142" s="2"/>
@@ -13383,8 +13878,11 @@
       <c r="CD142" s="2"/>
       <c r="CE142" s="2"/>
       <c r="CF142" s="2"/>
-    </row>
-    <row r="143" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG142" s="2"/>
+      <c r="CH142" s="2"/>
+      <c r="CI142" s="2"/>
+    </row>
+    <row r="143" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -13419,9 +13917,9 @@
       <c r="AF143" s="2"/>
       <c r="AG143" s="2"/>
       <c r="AH143" s="2"/>
-      <c r="AI143" s="2"/>
-      <c r="AJ143" s="2"/>
-      <c r="AK143" s="2"/>
+      <c r="AI143" s="8"/>
+      <c r="AJ143" s="8"/>
+      <c r="AK143" s="8"/>
       <c r="AL143" s="2"/>
       <c r="AM143" s="2"/>
       <c r="AN143" s="2"/>
@@ -13469,8 +13967,11 @@
       <c r="CD143" s="2"/>
       <c r="CE143" s="2"/>
       <c r="CF143" s="2"/>
-    </row>
-    <row r="144" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG143" s="2"/>
+      <c r="CH143" s="2"/>
+      <c r="CI143" s="2"/>
+    </row>
+    <row r="144" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -13505,9 +14006,9 @@
       <c r="AF144" s="2"/>
       <c r="AG144" s="2"/>
       <c r="AH144" s="2"/>
-      <c r="AI144" s="2"/>
-      <c r="AJ144" s="2"/>
-      <c r="AK144" s="2"/>
+      <c r="AI144" s="8"/>
+      <c r="AJ144" s="8"/>
+      <c r="AK144" s="8"/>
       <c r="AL144" s="2"/>
       <c r="AM144" s="2"/>
       <c r="AN144" s="2"/>
@@ -13555,8 +14056,11 @@
       <c r="CD144" s="2"/>
       <c r="CE144" s="2"/>
       <c r="CF144" s="2"/>
-    </row>
-    <row r="145" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG144" s="2"/>
+      <c r="CH144" s="2"/>
+      <c r="CI144" s="2"/>
+    </row>
+    <row r="145" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -13591,9 +14095,9 @@
       <c r="AF145" s="2"/>
       <c r="AG145" s="2"/>
       <c r="AH145" s="2"/>
-      <c r="AI145" s="2"/>
-      <c r="AJ145" s="2"/>
-      <c r="AK145" s="2"/>
+      <c r="AI145" s="8"/>
+      <c r="AJ145" s="8"/>
+      <c r="AK145" s="8"/>
       <c r="AL145" s="2"/>
       <c r="AM145" s="2"/>
       <c r="AN145" s="2"/>
@@ -13641,8 +14145,11 @@
       <c r="CD145" s="2"/>
       <c r="CE145" s="2"/>
       <c r="CF145" s="2"/>
-    </row>
-    <row r="146" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG145" s="2"/>
+      <c r="CH145" s="2"/>
+      <c r="CI145" s="2"/>
+    </row>
+    <row r="146" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -13677,9 +14184,9 @@
       <c r="AF146" s="2"/>
       <c r="AG146" s="2"/>
       <c r="AH146" s="2"/>
-      <c r="AI146" s="2"/>
-      <c r="AJ146" s="2"/>
-      <c r="AK146" s="2"/>
+      <c r="AI146" s="8"/>
+      <c r="AJ146" s="8"/>
+      <c r="AK146" s="8"/>
       <c r="AL146" s="2"/>
       <c r="AM146" s="2"/>
       <c r="AN146" s="2"/>
@@ -13727,8 +14234,11 @@
       <c r="CD146" s="2"/>
       <c r="CE146" s="2"/>
       <c r="CF146" s="2"/>
-    </row>
-    <row r="147" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG146" s="2"/>
+      <c r="CH146" s="2"/>
+      <c r="CI146" s="2"/>
+    </row>
+    <row r="147" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -13763,9 +14273,9 @@
       <c r="AF147" s="2"/>
       <c r="AG147" s="2"/>
       <c r="AH147" s="2"/>
-      <c r="AI147" s="2"/>
-      <c r="AJ147" s="2"/>
-      <c r="AK147" s="2"/>
+      <c r="AI147" s="8"/>
+      <c r="AJ147" s="8"/>
+      <c r="AK147" s="8"/>
       <c r="AL147" s="2"/>
       <c r="AM147" s="2"/>
       <c r="AN147" s="2"/>
@@ -13813,8 +14323,11 @@
       <c r="CD147" s="2"/>
       <c r="CE147" s="2"/>
       <c r="CF147" s="2"/>
-    </row>
-    <row r="148" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG147" s="2"/>
+      <c r="CH147" s="2"/>
+      <c r="CI147" s="2"/>
+    </row>
+    <row r="148" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -13849,9 +14362,9 @@
       <c r="AF148" s="2"/>
       <c r="AG148" s="2"/>
       <c r="AH148" s="2"/>
-      <c r="AI148" s="2"/>
-      <c r="AJ148" s="2"/>
-      <c r="AK148" s="2"/>
+      <c r="AI148" s="8"/>
+      <c r="AJ148" s="8"/>
+      <c r="AK148" s="8"/>
       <c r="AL148" s="2"/>
       <c r="AM148" s="2"/>
       <c r="AN148" s="2"/>
@@ -13899,8 +14412,11 @@
       <c r="CD148" s="2"/>
       <c r="CE148" s="2"/>
       <c r="CF148" s="2"/>
-    </row>
-    <row r="149" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG148" s="2"/>
+      <c r="CH148" s="2"/>
+      <c r="CI148" s="2"/>
+    </row>
+    <row r="149" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -13935,9 +14451,9 @@
       <c r="AF149" s="2"/>
       <c r="AG149" s="2"/>
       <c r="AH149" s="2"/>
-      <c r="AI149" s="2"/>
-      <c r="AJ149" s="2"/>
-      <c r="AK149" s="2"/>
+      <c r="AI149" s="8"/>
+      <c r="AJ149" s="8"/>
+      <c r="AK149" s="8"/>
       <c r="AL149" s="2"/>
       <c r="AM149" s="2"/>
       <c r="AN149" s="2"/>
@@ -13985,8 +14501,11 @@
       <c r="CD149" s="2"/>
       <c r="CE149" s="2"/>
       <c r="CF149" s="2"/>
-    </row>
-    <row r="150" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG149" s="2"/>
+      <c r="CH149" s="2"/>
+      <c r="CI149" s="2"/>
+    </row>
+    <row r="150" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -14021,9 +14540,9 @@
       <c r="AF150" s="2"/>
       <c r="AG150" s="2"/>
       <c r="AH150" s="2"/>
-      <c r="AI150" s="2"/>
-      <c r="AJ150" s="2"/>
-      <c r="AK150" s="2"/>
+      <c r="AI150" s="8"/>
+      <c r="AJ150" s="8"/>
+      <c r="AK150" s="8"/>
       <c r="AL150" s="2"/>
       <c r="AM150" s="2"/>
       <c r="AN150" s="2"/>
@@ -14071,8 +14590,11 @@
       <c r="CD150" s="2"/>
       <c r="CE150" s="2"/>
       <c r="CF150" s="2"/>
-    </row>
-    <row r="151" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG150" s="2"/>
+      <c r="CH150" s="2"/>
+      <c r="CI150" s="2"/>
+    </row>
+    <row r="151" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -14107,9 +14629,9 @@
       <c r="AF151" s="2"/>
       <c r="AG151" s="2"/>
       <c r="AH151" s="2"/>
-      <c r="AI151" s="2"/>
-      <c r="AJ151" s="2"/>
-      <c r="AK151" s="2"/>
+      <c r="AI151" s="8"/>
+      <c r="AJ151" s="8"/>
+      <c r="AK151" s="8"/>
       <c r="AL151" s="2"/>
       <c r="AM151" s="2"/>
       <c r="AN151" s="2"/>
@@ -14157,8 +14679,11 @@
       <c r="CD151" s="2"/>
       <c r="CE151" s="2"/>
       <c r="CF151" s="2"/>
-    </row>
-    <row r="152" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG151" s="2"/>
+      <c r="CH151" s="2"/>
+      <c r="CI151" s="2"/>
+    </row>
+    <row r="152" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -14193,9 +14718,9 @@
       <c r="AF152" s="2"/>
       <c r="AG152" s="2"/>
       <c r="AH152" s="2"/>
-      <c r="AI152" s="2"/>
-      <c r="AJ152" s="2"/>
-      <c r="AK152" s="2"/>
+      <c r="AI152" s="8"/>
+      <c r="AJ152" s="8"/>
+      <c r="AK152" s="8"/>
       <c r="AL152" s="2"/>
       <c r="AM152" s="2"/>
       <c r="AN152" s="2"/>
@@ -14243,8 +14768,11 @@
       <c r="CD152" s="2"/>
       <c r="CE152" s="2"/>
       <c r="CF152" s="2"/>
-    </row>
-    <row r="153" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG152" s="2"/>
+      <c r="CH152" s="2"/>
+      <c r="CI152" s="2"/>
+    </row>
+    <row r="153" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -14279,9 +14807,9 @@
       <c r="AF153" s="2"/>
       <c r="AG153" s="2"/>
       <c r="AH153" s="2"/>
-      <c r="AI153" s="2"/>
-      <c r="AJ153" s="2"/>
-      <c r="AK153" s="2"/>
+      <c r="AI153" s="8"/>
+      <c r="AJ153" s="8"/>
+      <c r="AK153" s="8"/>
       <c r="AL153" s="2"/>
       <c r="AM153" s="2"/>
       <c r="AN153" s="2"/>
@@ -14329,8 +14857,11 @@
       <c r="CD153" s="2"/>
       <c r="CE153" s="2"/>
       <c r="CF153" s="2"/>
-    </row>
-    <row r="154" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG153" s="2"/>
+      <c r="CH153" s="2"/>
+      <c r="CI153" s="2"/>
+    </row>
+    <row r="154" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -14365,9 +14896,9 @@
       <c r="AF154" s="2"/>
       <c r="AG154" s="2"/>
       <c r="AH154" s="2"/>
-      <c r="AI154" s="2"/>
-      <c r="AJ154" s="2"/>
-      <c r="AK154" s="2"/>
+      <c r="AI154" s="8"/>
+      <c r="AJ154" s="8"/>
+      <c r="AK154" s="8"/>
       <c r="AL154" s="2"/>
       <c r="AM154" s="2"/>
       <c r="AN154" s="2"/>
@@ -14415,8 +14946,11 @@
       <c r="CD154" s="2"/>
       <c r="CE154" s="2"/>
       <c r="CF154" s="2"/>
-    </row>
-    <row r="155" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG154" s="2"/>
+      <c r="CH154" s="2"/>
+      <c r="CI154" s="2"/>
+    </row>
+    <row r="155" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -14451,9 +14985,9 @@
       <c r="AF155" s="2"/>
       <c r="AG155" s="2"/>
       <c r="AH155" s="2"/>
-      <c r="AI155" s="2"/>
-      <c r="AJ155" s="2"/>
-      <c r="AK155" s="2"/>
+      <c r="AI155" s="8"/>
+      <c r="AJ155" s="8"/>
+      <c r="AK155" s="8"/>
       <c r="AL155" s="2"/>
       <c r="AM155" s="2"/>
       <c r="AN155" s="2"/>
@@ -14501,8 +15035,11 @@
       <c r="CD155" s="2"/>
       <c r="CE155" s="2"/>
       <c r="CF155" s="2"/>
-    </row>
-    <row r="156" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG155" s="2"/>
+      <c r="CH155" s="2"/>
+      <c r="CI155" s="2"/>
+    </row>
+    <row r="156" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -14537,9 +15074,9 @@
       <c r="AF156" s="2"/>
       <c r="AG156" s="2"/>
       <c r="AH156" s="2"/>
-      <c r="AI156" s="2"/>
-      <c r="AJ156" s="2"/>
-      <c r="AK156" s="2"/>
+      <c r="AI156" s="8"/>
+      <c r="AJ156" s="8"/>
+      <c r="AK156" s="8"/>
       <c r="AL156" s="2"/>
       <c r="AM156" s="2"/>
       <c r="AN156" s="2"/>
@@ -14587,8 +15124,11 @@
       <c r="CD156" s="2"/>
       <c r="CE156" s="2"/>
       <c r="CF156" s="2"/>
-    </row>
-    <row r="157" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG156" s="2"/>
+      <c r="CH156" s="2"/>
+      <c r="CI156" s="2"/>
+    </row>
+    <row r="157" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -14623,9 +15163,9 @@
       <c r="AF157" s="2"/>
       <c r="AG157" s="2"/>
       <c r="AH157" s="2"/>
-      <c r="AI157" s="2"/>
-      <c r="AJ157" s="2"/>
-      <c r="AK157" s="2"/>
+      <c r="AI157" s="8"/>
+      <c r="AJ157" s="8"/>
+      <c r="AK157" s="8"/>
       <c r="AL157" s="2"/>
       <c r="AM157" s="2"/>
       <c r="AN157" s="2"/>
@@ -14673,8 +15213,11 @@
       <c r="CD157" s="2"/>
       <c r="CE157" s="2"/>
       <c r="CF157" s="2"/>
-    </row>
-    <row r="158" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG157" s="2"/>
+      <c r="CH157" s="2"/>
+      <c r="CI157" s="2"/>
+    </row>
+    <row r="158" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -14709,9 +15252,9 @@
       <c r="AF158" s="2"/>
       <c r="AG158" s="2"/>
       <c r="AH158" s="2"/>
-      <c r="AI158" s="2"/>
-      <c r="AJ158" s="2"/>
-      <c r="AK158" s="2"/>
+      <c r="AI158" s="8"/>
+      <c r="AJ158" s="8"/>
+      <c r="AK158" s="8"/>
       <c r="AL158" s="2"/>
       <c r="AM158" s="2"/>
       <c r="AN158" s="2"/>
@@ -14759,8 +15302,11 @@
       <c r="CD158" s="2"/>
       <c r="CE158" s="2"/>
       <c r="CF158" s="2"/>
-    </row>
-    <row r="159" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG158" s="2"/>
+      <c r="CH158" s="2"/>
+      <c r="CI158" s="2"/>
+    </row>
+    <row r="159" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -14795,9 +15341,9 @@
       <c r="AF159" s="2"/>
       <c r="AG159" s="2"/>
       <c r="AH159" s="2"/>
-      <c r="AI159" s="2"/>
-      <c r="AJ159" s="2"/>
-      <c r="AK159" s="2"/>
+      <c r="AI159" s="8"/>
+      <c r="AJ159" s="8"/>
+      <c r="AK159" s="8"/>
       <c r="AL159" s="2"/>
       <c r="AM159" s="2"/>
       <c r="AN159" s="2"/>
@@ -14845,8 +15391,11 @@
       <c r="CD159" s="2"/>
       <c r="CE159" s="2"/>
       <c r="CF159" s="2"/>
-    </row>
-    <row r="160" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG159" s="2"/>
+      <c r="CH159" s="2"/>
+      <c r="CI159" s="2"/>
+    </row>
+    <row r="160" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -14881,9 +15430,9 @@
       <c r="AF160" s="2"/>
       <c r="AG160" s="2"/>
       <c r="AH160" s="2"/>
-      <c r="AI160" s="2"/>
-      <c r="AJ160" s="2"/>
-      <c r="AK160" s="2"/>
+      <c r="AI160" s="8"/>
+      <c r="AJ160" s="8"/>
+      <c r="AK160" s="8"/>
       <c r="AL160" s="2"/>
       <c r="AM160" s="2"/>
       <c r="AN160" s="2"/>
@@ -14931,8 +15480,11 @@
       <c r="CD160" s="2"/>
       <c r="CE160" s="2"/>
       <c r="CF160" s="2"/>
-    </row>
-    <row r="161" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG160" s="2"/>
+      <c r="CH160" s="2"/>
+      <c r="CI160" s="2"/>
+    </row>
+    <row r="161" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -14967,9 +15519,9 @@
       <c r="AF161" s="2"/>
       <c r="AG161" s="2"/>
       <c r="AH161" s="2"/>
-      <c r="AI161" s="2"/>
-      <c r="AJ161" s="2"/>
-      <c r="AK161" s="2"/>
+      <c r="AI161" s="8"/>
+      <c r="AJ161" s="8"/>
+      <c r="AK161" s="8"/>
       <c r="AL161" s="2"/>
       <c r="AM161" s="2"/>
       <c r="AN161" s="2"/>
@@ -15017,8 +15569,11 @@
       <c r="CD161" s="2"/>
       <c r="CE161" s="2"/>
       <c r="CF161" s="2"/>
-    </row>
-    <row r="162" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG161" s="2"/>
+      <c r="CH161" s="2"/>
+      <c r="CI161" s="2"/>
+    </row>
+    <row r="162" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -15053,9 +15608,9 @@
       <c r="AF162" s="2"/>
       <c r="AG162" s="2"/>
       <c r="AH162" s="2"/>
-      <c r="AI162" s="2"/>
-      <c r="AJ162" s="2"/>
-      <c r="AK162" s="2"/>
+      <c r="AI162" s="8"/>
+      <c r="AJ162" s="8"/>
+      <c r="AK162" s="8"/>
       <c r="AL162" s="2"/>
       <c r="AM162" s="2"/>
       <c r="AN162" s="2"/>
@@ -15103,8 +15658,11 @@
       <c r="CD162" s="2"/>
       <c r="CE162" s="2"/>
       <c r="CF162" s="2"/>
-    </row>
-    <row r="163" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG162" s="2"/>
+      <c r="CH162" s="2"/>
+      <c r="CI162" s="2"/>
+    </row>
+    <row r="163" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -15139,9 +15697,9 @@
       <c r="AF163" s="2"/>
       <c r="AG163" s="2"/>
       <c r="AH163" s="2"/>
-      <c r="AI163" s="2"/>
-      <c r="AJ163" s="2"/>
-      <c r="AK163" s="2"/>
+      <c r="AI163" s="8"/>
+      <c r="AJ163" s="8"/>
+      <c r="AK163" s="8"/>
       <c r="AL163" s="2"/>
       <c r="AM163" s="2"/>
       <c r="AN163" s="2"/>
@@ -15189,8 +15747,11 @@
       <c r="CD163" s="2"/>
       <c r="CE163" s="2"/>
       <c r="CF163" s="2"/>
-    </row>
-    <row r="164" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG163" s="2"/>
+      <c r="CH163" s="2"/>
+      <c r="CI163" s="2"/>
+    </row>
+    <row r="164" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -15225,9 +15786,9 @@
       <c r="AF164" s="2"/>
       <c r="AG164" s="2"/>
       <c r="AH164" s="2"/>
-      <c r="AI164" s="2"/>
-      <c r="AJ164" s="2"/>
-      <c r="AK164" s="2"/>
+      <c r="AI164" s="8"/>
+      <c r="AJ164" s="8"/>
+      <c r="AK164" s="8"/>
       <c r="AL164" s="2"/>
       <c r="AM164" s="2"/>
       <c r="AN164" s="2"/>
@@ -15275,8 +15836,11 @@
       <c r="CD164" s="2"/>
       <c r="CE164" s="2"/>
       <c r="CF164" s="2"/>
-    </row>
-    <row r="165" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG164" s="2"/>
+      <c r="CH164" s="2"/>
+      <c r="CI164" s="2"/>
+    </row>
+    <row r="165" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -15311,9 +15875,9 @@
       <c r="AF165" s="2"/>
       <c r="AG165" s="2"/>
       <c r="AH165" s="2"/>
-      <c r="AI165" s="2"/>
-      <c r="AJ165" s="2"/>
-      <c r="AK165" s="2"/>
+      <c r="AI165" s="8"/>
+      <c r="AJ165" s="8"/>
+      <c r="AK165" s="8"/>
       <c r="AL165" s="2"/>
       <c r="AM165" s="2"/>
       <c r="AN165" s="2"/>
@@ -15361,8 +15925,11 @@
       <c r="CD165" s="2"/>
       <c r="CE165" s="2"/>
       <c r="CF165" s="2"/>
-    </row>
-    <row r="166" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG165" s="2"/>
+      <c r="CH165" s="2"/>
+      <c r="CI165" s="2"/>
+    </row>
+    <row r="166" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -15397,9 +15964,9 @@
       <c r="AF166" s="2"/>
       <c r="AG166" s="2"/>
       <c r="AH166" s="2"/>
-      <c r="AI166" s="2"/>
-      <c r="AJ166" s="2"/>
-      <c r="AK166" s="2"/>
+      <c r="AI166" s="8"/>
+      <c r="AJ166" s="8"/>
+      <c r="AK166" s="8"/>
       <c r="AL166" s="2"/>
       <c r="AM166" s="2"/>
       <c r="AN166" s="2"/>
@@ -15447,8 +16014,11 @@
       <c r="CD166" s="2"/>
       <c r="CE166" s="2"/>
       <c r="CF166" s="2"/>
-    </row>
-    <row r="167" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG166" s="2"/>
+      <c r="CH166" s="2"/>
+      <c r="CI166" s="2"/>
+    </row>
+    <row r="167" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -15483,9 +16053,9 @@
       <c r="AF167" s="2"/>
       <c r="AG167" s="2"/>
       <c r="AH167" s="2"/>
-      <c r="AI167" s="2"/>
-      <c r="AJ167" s="2"/>
-      <c r="AK167" s="2"/>
+      <c r="AI167" s="8"/>
+      <c r="AJ167" s="8"/>
+      <c r="AK167" s="8"/>
       <c r="AL167" s="2"/>
       <c r="AM167" s="2"/>
       <c r="AN167" s="2"/>
@@ -15533,8 +16103,11 @@
       <c r="CD167" s="2"/>
       <c r="CE167" s="2"/>
       <c r="CF167" s="2"/>
-    </row>
-    <row r="168" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG167" s="2"/>
+      <c r="CH167" s="2"/>
+      <c r="CI167" s="2"/>
+    </row>
+    <row r="168" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -15569,9 +16142,9 @@
       <c r="AF168" s="2"/>
       <c r="AG168" s="2"/>
       <c r="AH168" s="2"/>
-      <c r="AI168" s="2"/>
-      <c r="AJ168" s="2"/>
-      <c r="AK168" s="2"/>
+      <c r="AI168" s="8"/>
+      <c r="AJ168" s="8"/>
+      <c r="AK168" s="8"/>
       <c r="AL168" s="2"/>
       <c r="AM168" s="2"/>
       <c r="AN168" s="2"/>
@@ -15619,8 +16192,11 @@
       <c r="CD168" s="2"/>
       <c r="CE168" s="2"/>
       <c r="CF168" s="2"/>
-    </row>
-    <row r="169" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG168" s="2"/>
+      <c r="CH168" s="2"/>
+      <c r="CI168" s="2"/>
+    </row>
+    <row r="169" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -15655,9 +16231,9 @@
       <c r="AF169" s="2"/>
       <c r="AG169" s="2"/>
       <c r="AH169" s="2"/>
-      <c r="AI169" s="2"/>
-      <c r="AJ169" s="2"/>
-      <c r="AK169" s="2"/>
+      <c r="AI169" s="8"/>
+      <c r="AJ169" s="8"/>
+      <c r="AK169" s="8"/>
       <c r="AL169" s="2"/>
       <c r="AM169" s="2"/>
       <c r="AN169" s="2"/>
@@ -15705,8 +16281,11 @@
       <c r="CD169" s="2"/>
       <c r="CE169" s="2"/>
       <c r="CF169" s="2"/>
-    </row>
-    <row r="170" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG169" s="2"/>
+      <c r="CH169" s="2"/>
+      <c r="CI169" s="2"/>
+    </row>
+    <row r="170" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -15741,9 +16320,9 @@
       <c r="AF170" s="2"/>
       <c r="AG170" s="2"/>
       <c r="AH170" s="2"/>
-      <c r="AI170" s="2"/>
-      <c r="AJ170" s="2"/>
-      <c r="AK170" s="2"/>
+      <c r="AI170" s="8"/>
+      <c r="AJ170" s="8"/>
+      <c r="AK170" s="8"/>
       <c r="AL170" s="2"/>
       <c r="AM170" s="2"/>
       <c r="AN170" s="2"/>
@@ -15791,8 +16370,11 @@
       <c r="CD170" s="2"/>
       <c r="CE170" s="2"/>
       <c r="CF170" s="2"/>
-    </row>
-    <row r="171" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG170" s="2"/>
+      <c r="CH170" s="2"/>
+      <c r="CI170" s="2"/>
+    </row>
+    <row r="171" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -15827,9 +16409,9 @@
       <c r="AF171" s="2"/>
       <c r="AG171" s="2"/>
       <c r="AH171" s="2"/>
-      <c r="AI171" s="2"/>
-      <c r="AJ171" s="2"/>
-      <c r="AK171" s="2"/>
+      <c r="AI171" s="8"/>
+      <c r="AJ171" s="8"/>
+      <c r="AK171" s="8"/>
       <c r="AL171" s="2"/>
       <c r="AM171" s="2"/>
       <c r="AN171" s="2"/>
@@ -15877,8 +16459,11 @@
       <c r="CD171" s="2"/>
       <c r="CE171" s="2"/>
       <c r="CF171" s="2"/>
-    </row>
-    <row r="172" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG171" s="2"/>
+      <c r="CH171" s="2"/>
+      <c r="CI171" s="2"/>
+    </row>
+    <row r="172" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -15913,9 +16498,9 @@
       <c r="AF172" s="2"/>
       <c r="AG172" s="2"/>
       <c r="AH172" s="2"/>
-      <c r="AI172" s="2"/>
-      <c r="AJ172" s="2"/>
-      <c r="AK172" s="2"/>
+      <c r="AI172" s="8"/>
+      <c r="AJ172" s="8"/>
+      <c r="AK172" s="8"/>
       <c r="AL172" s="2"/>
       <c r="AM172" s="2"/>
       <c r="AN172" s="2"/>
@@ -15963,8 +16548,11 @@
       <c r="CD172" s="2"/>
       <c r="CE172" s="2"/>
       <c r="CF172" s="2"/>
-    </row>
-    <row r="173" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG172" s="2"/>
+      <c r="CH172" s="2"/>
+      <c r="CI172" s="2"/>
+    </row>
+    <row r="173" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -15999,9 +16587,9 @@
       <c r="AF173" s="2"/>
       <c r="AG173" s="2"/>
       <c r="AH173" s="2"/>
-      <c r="AI173" s="2"/>
-      <c r="AJ173" s="2"/>
-      <c r="AK173" s="2"/>
+      <c r="AI173" s="8"/>
+      <c r="AJ173" s="8"/>
+      <c r="AK173" s="8"/>
       <c r="AL173" s="2"/>
       <c r="AM173" s="2"/>
       <c r="AN173" s="2"/>
@@ -16049,8 +16637,11 @@
       <c r="CD173" s="2"/>
       <c r="CE173" s="2"/>
       <c r="CF173" s="2"/>
-    </row>
-    <row r="174" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG173" s="2"/>
+      <c r="CH173" s="2"/>
+      <c r="CI173" s="2"/>
+    </row>
+    <row r="174" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -16085,9 +16676,9 @@
       <c r="AF174" s="2"/>
       <c r="AG174" s="2"/>
       <c r="AH174" s="2"/>
-      <c r="AI174" s="2"/>
-      <c r="AJ174" s="2"/>
-      <c r="AK174" s="2"/>
+      <c r="AI174" s="8"/>
+      <c r="AJ174" s="8"/>
+      <c r="AK174" s="8"/>
       <c r="AL174" s="2"/>
       <c r="AM174" s="2"/>
       <c r="AN174" s="2"/>
@@ -16135,8 +16726,11 @@
       <c r="CD174" s="2"/>
       <c r="CE174" s="2"/>
       <c r="CF174" s="2"/>
-    </row>
-    <row r="175" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG174" s="2"/>
+      <c r="CH174" s="2"/>
+      <c r="CI174" s="2"/>
+    </row>
+    <row r="175" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -16171,9 +16765,9 @@
       <c r="AF175" s="2"/>
       <c r="AG175" s="2"/>
       <c r="AH175" s="2"/>
-      <c r="AI175" s="2"/>
-      <c r="AJ175" s="2"/>
-      <c r="AK175" s="2"/>
+      <c r="AI175" s="8"/>
+      <c r="AJ175" s="8"/>
+      <c r="AK175" s="8"/>
       <c r="AL175" s="2"/>
       <c r="AM175" s="2"/>
       <c r="AN175" s="2"/>
@@ -16221,8 +16815,11 @@
       <c r="CD175" s="2"/>
       <c r="CE175" s="2"/>
       <c r="CF175" s="2"/>
-    </row>
-    <row r="176" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG175" s="2"/>
+      <c r="CH175" s="2"/>
+      <c r="CI175" s="2"/>
+    </row>
+    <row r="176" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -16257,9 +16854,9 @@
       <c r="AF176" s="2"/>
       <c r="AG176" s="2"/>
       <c r="AH176" s="2"/>
-      <c r="AI176" s="2"/>
-      <c r="AJ176" s="2"/>
-      <c r="AK176" s="2"/>
+      <c r="AI176" s="8"/>
+      <c r="AJ176" s="8"/>
+      <c r="AK176" s="8"/>
       <c r="AL176" s="2"/>
       <c r="AM176" s="2"/>
       <c r="AN176" s="2"/>
@@ -16307,8 +16904,11 @@
       <c r="CD176" s="2"/>
       <c r="CE176" s="2"/>
       <c r="CF176" s="2"/>
-    </row>
-    <row r="177" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG176" s="2"/>
+      <c r="CH176" s="2"/>
+      <c r="CI176" s="2"/>
+    </row>
+    <row r="177" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -16343,9 +16943,9 @@
       <c r="AF177" s="2"/>
       <c r="AG177" s="2"/>
       <c r="AH177" s="2"/>
-      <c r="AI177" s="2"/>
-      <c r="AJ177" s="2"/>
-      <c r="AK177" s="2"/>
+      <c r="AI177" s="8"/>
+      <c r="AJ177" s="8"/>
+      <c r="AK177" s="8"/>
       <c r="AL177" s="2"/>
       <c r="AM177" s="2"/>
       <c r="AN177" s="2"/>
@@ -16393,8 +16993,11 @@
       <c r="CD177" s="2"/>
       <c r="CE177" s="2"/>
       <c r="CF177" s="2"/>
-    </row>
-    <row r="178" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG177" s="2"/>
+      <c r="CH177" s="2"/>
+      <c r="CI177" s="2"/>
+    </row>
+    <row r="178" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -16429,9 +17032,9 @@
       <c r="AF178" s="2"/>
       <c r="AG178" s="2"/>
       <c r="AH178" s="2"/>
-      <c r="AI178" s="2"/>
-      <c r="AJ178" s="2"/>
-      <c r="AK178" s="2"/>
+      <c r="AI178" s="8"/>
+      <c r="AJ178" s="8"/>
+      <c r="AK178" s="8"/>
       <c r="AL178" s="2"/>
       <c r="AM178" s="2"/>
       <c r="AN178" s="2"/>
@@ -16479,8 +17082,11 @@
       <c r="CD178" s="2"/>
       <c r="CE178" s="2"/>
       <c r="CF178" s="2"/>
-    </row>
-    <row r="179" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG178" s="2"/>
+      <c r="CH178" s="2"/>
+      <c r="CI178" s="2"/>
+    </row>
+    <row r="179" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -16515,9 +17121,9 @@
       <c r="AF179" s="2"/>
       <c r="AG179" s="2"/>
       <c r="AH179" s="2"/>
-      <c r="AI179" s="2"/>
-      <c r="AJ179" s="2"/>
-      <c r="AK179" s="2"/>
+      <c r="AI179" s="8"/>
+      <c r="AJ179" s="8"/>
+      <c r="AK179" s="8"/>
       <c r="AL179" s="2"/>
       <c r="AM179" s="2"/>
       <c r="AN179" s="2"/>
@@ -16565,8 +17171,11 @@
       <c r="CD179" s="2"/>
       <c r="CE179" s="2"/>
       <c r="CF179" s="2"/>
-    </row>
-    <row r="180" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG179" s="2"/>
+      <c r="CH179" s="2"/>
+      <c r="CI179" s="2"/>
+    </row>
+    <row r="180" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -16601,9 +17210,9 @@
       <c r="AF180" s="2"/>
       <c r="AG180" s="2"/>
       <c r="AH180" s="2"/>
-      <c r="AI180" s="2"/>
-      <c r="AJ180" s="2"/>
-      <c r="AK180" s="2"/>
+      <c r="AI180" s="8"/>
+      <c r="AJ180" s="8"/>
+      <c r="AK180" s="8"/>
       <c r="AL180" s="2"/>
       <c r="AM180" s="2"/>
       <c r="AN180" s="2"/>
@@ -16651,8 +17260,11 @@
       <c r="CD180" s="2"/>
       <c r="CE180" s="2"/>
       <c r="CF180" s="2"/>
-    </row>
-    <row r="181" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG180" s="2"/>
+      <c r="CH180" s="2"/>
+      <c r="CI180" s="2"/>
+    </row>
+    <row r="181" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -16687,9 +17299,9 @@
       <c r="AF181" s="2"/>
       <c r="AG181" s="2"/>
       <c r="AH181" s="2"/>
-      <c r="AI181" s="2"/>
-      <c r="AJ181" s="2"/>
-      <c r="AK181" s="2"/>
+      <c r="AI181" s="8"/>
+      <c r="AJ181" s="8"/>
+      <c r="AK181" s="8"/>
       <c r="AL181" s="2"/>
       <c r="AM181" s="2"/>
       <c r="AN181" s="2"/>
@@ -16737,8 +17349,11 @@
       <c r="CD181" s="2"/>
       <c r="CE181" s="2"/>
       <c r="CF181" s="2"/>
-    </row>
-    <row r="182" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG181" s="2"/>
+      <c r="CH181" s="2"/>
+      <c r="CI181" s="2"/>
+    </row>
+    <row r="182" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -16773,9 +17388,9 @@
       <c r="AF182" s="2"/>
       <c r="AG182" s="2"/>
       <c r="AH182" s="2"/>
-      <c r="AI182" s="2"/>
-      <c r="AJ182" s="2"/>
-      <c r="AK182" s="2"/>
+      <c r="AI182" s="8"/>
+      <c r="AJ182" s="8"/>
+      <c r="AK182" s="8"/>
       <c r="AL182" s="2"/>
       <c r="AM182" s="2"/>
       <c r="AN182" s="2"/>
@@ -16823,8 +17438,11 @@
       <c r="CD182" s="2"/>
       <c r="CE182" s="2"/>
       <c r="CF182" s="2"/>
-    </row>
-    <row r="183" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG182" s="2"/>
+      <c r="CH182" s="2"/>
+      <c r="CI182" s="2"/>
+    </row>
+    <row r="183" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -16859,9 +17477,9 @@
       <c r="AF183" s="2"/>
       <c r="AG183" s="2"/>
       <c r="AH183" s="2"/>
-      <c r="AI183" s="2"/>
-      <c r="AJ183" s="2"/>
-      <c r="AK183" s="2"/>
+      <c r="AI183" s="8"/>
+      <c r="AJ183" s="8"/>
+      <c r="AK183" s="8"/>
       <c r="AL183" s="2"/>
       <c r="AM183" s="2"/>
       <c r="AN183" s="2"/>
@@ -16909,8 +17527,11 @@
       <c r="CD183" s="2"/>
       <c r="CE183" s="2"/>
       <c r="CF183" s="2"/>
-    </row>
-    <row r="184" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG183" s="2"/>
+      <c r="CH183" s="2"/>
+      <c r="CI183" s="2"/>
+    </row>
+    <row r="184" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -16945,9 +17566,9 @@
       <c r="AF184" s="2"/>
       <c r="AG184" s="2"/>
       <c r="AH184" s="2"/>
-      <c r="AI184" s="2"/>
-      <c r="AJ184" s="2"/>
-      <c r="AK184" s="2"/>
+      <c r="AI184" s="8"/>
+      <c r="AJ184" s="8"/>
+      <c r="AK184" s="8"/>
       <c r="AL184" s="2"/>
       <c r="AM184" s="2"/>
       <c r="AN184" s="2"/>
@@ -16995,8 +17616,11 @@
       <c r="CD184" s="2"/>
       <c r="CE184" s="2"/>
       <c r="CF184" s="2"/>
-    </row>
-    <row r="185" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG184" s="2"/>
+      <c r="CH184" s="2"/>
+      <c r="CI184" s="2"/>
+    </row>
+    <row r="185" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -17031,9 +17655,9 @@
       <c r="AF185" s="2"/>
       <c r="AG185" s="2"/>
       <c r="AH185" s="2"/>
-      <c r="AI185" s="2"/>
-      <c r="AJ185" s="2"/>
-      <c r="AK185" s="2"/>
+      <c r="AI185" s="8"/>
+      <c r="AJ185" s="8"/>
+      <c r="AK185" s="8"/>
       <c r="AL185" s="2"/>
       <c r="AM185" s="2"/>
       <c r="AN185" s="2"/>
@@ -17081,8 +17705,11 @@
       <c r="CD185" s="2"/>
       <c r="CE185" s="2"/>
       <c r="CF185" s="2"/>
-    </row>
-    <row r="186" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG185" s="2"/>
+      <c r="CH185" s="2"/>
+      <c r="CI185" s="2"/>
+    </row>
+    <row r="186" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -17117,9 +17744,9 @@
       <c r="AF186" s="2"/>
       <c r="AG186" s="2"/>
       <c r="AH186" s="2"/>
-      <c r="AI186" s="2"/>
-      <c r="AJ186" s="2"/>
-      <c r="AK186" s="2"/>
+      <c r="AI186" s="8"/>
+      <c r="AJ186" s="8"/>
+      <c r="AK186" s="8"/>
       <c r="AL186" s="2"/>
       <c r="AM186" s="2"/>
       <c r="AN186" s="2"/>
@@ -17167,8 +17794,11 @@
       <c r="CD186" s="2"/>
       <c r="CE186" s="2"/>
       <c r="CF186" s="2"/>
-    </row>
-    <row r="187" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG186" s="2"/>
+      <c r="CH186" s="2"/>
+      <c r="CI186" s="2"/>
+    </row>
+    <row r="187" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -17203,9 +17833,9 @@
       <c r="AF187" s="2"/>
       <c r="AG187" s="2"/>
       <c r="AH187" s="2"/>
-      <c r="AI187" s="2"/>
-      <c r="AJ187" s="2"/>
-      <c r="AK187" s="2"/>
+      <c r="AI187" s="8"/>
+      <c r="AJ187" s="8"/>
+      <c r="AK187" s="8"/>
       <c r="AL187" s="2"/>
       <c r="AM187" s="2"/>
       <c r="AN187" s="2"/>
@@ -17253,8 +17883,11 @@
       <c r="CD187" s="2"/>
       <c r="CE187" s="2"/>
       <c r="CF187" s="2"/>
-    </row>
-    <row r="188" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG187" s="2"/>
+      <c r="CH187" s="2"/>
+      <c r="CI187" s="2"/>
+    </row>
+    <row r="188" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -17289,9 +17922,9 @@
       <c r="AF188" s="2"/>
       <c r="AG188" s="2"/>
       <c r="AH188" s="2"/>
-      <c r="AI188" s="2"/>
-      <c r="AJ188" s="2"/>
-      <c r="AK188" s="2"/>
+      <c r="AI188" s="8"/>
+      <c r="AJ188" s="8"/>
+      <c r="AK188" s="8"/>
       <c r="AL188" s="2"/>
       <c r="AM188" s="2"/>
       <c r="AN188" s="2"/>
@@ -17339,8 +17972,11 @@
       <c r="CD188" s="2"/>
       <c r="CE188" s="2"/>
       <c r="CF188" s="2"/>
-    </row>
-    <row r="189" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG188" s="2"/>
+      <c r="CH188" s="2"/>
+      <c r="CI188" s="2"/>
+    </row>
+    <row r="189" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -17375,9 +18011,9 @@
       <c r="AF189" s="2"/>
       <c r="AG189" s="2"/>
       <c r="AH189" s="2"/>
-      <c r="AI189" s="2"/>
-      <c r="AJ189" s="2"/>
-      <c r="AK189" s="2"/>
+      <c r="AI189" s="8"/>
+      <c r="AJ189" s="8"/>
+      <c r="AK189" s="8"/>
       <c r="AL189" s="2"/>
       <c r="AM189" s="2"/>
       <c r="AN189" s="2"/>
@@ -17425,8 +18061,11 @@
       <c r="CD189" s="2"/>
       <c r="CE189" s="2"/>
       <c r="CF189" s="2"/>
-    </row>
-    <row r="190" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG189" s="2"/>
+      <c r="CH189" s="2"/>
+      <c r="CI189" s="2"/>
+    </row>
+    <row r="190" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -17461,9 +18100,9 @@
       <c r="AF190" s="2"/>
       <c r="AG190" s="2"/>
       <c r="AH190" s="2"/>
-      <c r="AI190" s="2"/>
-      <c r="AJ190" s="2"/>
-      <c r="AK190" s="2"/>
+      <c r="AI190" s="8"/>
+      <c r="AJ190" s="8"/>
+      <c r="AK190" s="8"/>
       <c r="AL190" s="2"/>
       <c r="AM190" s="2"/>
       <c r="AN190" s="2"/>
@@ -17511,8 +18150,11 @@
       <c r="CD190" s="2"/>
       <c r="CE190" s="2"/>
       <c r="CF190" s="2"/>
-    </row>
-    <row r="191" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG190" s="2"/>
+      <c r="CH190" s="2"/>
+      <c r="CI190" s="2"/>
+    </row>
+    <row r="191" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -17547,9 +18189,9 @@
       <c r="AF191" s="2"/>
       <c r="AG191" s="2"/>
       <c r="AH191" s="2"/>
-      <c r="AI191" s="2"/>
-      <c r="AJ191" s="2"/>
-      <c r="AK191" s="2"/>
+      <c r="AI191" s="8"/>
+      <c r="AJ191" s="8"/>
+      <c r="AK191" s="8"/>
       <c r="AL191" s="2"/>
       <c r="AM191" s="2"/>
       <c r="AN191" s="2"/>
@@ -17597,8 +18239,11 @@
       <c r="CD191" s="2"/>
       <c r="CE191" s="2"/>
       <c r="CF191" s="2"/>
-    </row>
-    <row r="192" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG191" s="2"/>
+      <c r="CH191" s="2"/>
+      <c r="CI191" s="2"/>
+    </row>
+    <row r="192" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -17633,9 +18278,9 @@
       <c r="AF192" s="2"/>
       <c r="AG192" s="2"/>
       <c r="AH192" s="2"/>
-      <c r="AI192" s="2"/>
-      <c r="AJ192" s="2"/>
-      <c r="AK192" s="2"/>
+      <c r="AI192" s="8"/>
+      <c r="AJ192" s="8"/>
+      <c r="AK192" s="8"/>
       <c r="AL192" s="2"/>
       <c r="AM192" s="2"/>
       <c r="AN192" s="2"/>
@@ -17683,8 +18328,11 @@
       <c r="CD192" s="2"/>
       <c r="CE192" s="2"/>
       <c r="CF192" s="2"/>
-    </row>
-    <row r="193" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG192" s="2"/>
+      <c r="CH192" s="2"/>
+      <c r="CI192" s="2"/>
+    </row>
+    <row r="193" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -17719,9 +18367,9 @@
       <c r="AF193" s="2"/>
       <c r="AG193" s="2"/>
       <c r="AH193" s="2"/>
-      <c r="AI193" s="2"/>
-      <c r="AJ193" s="2"/>
-      <c r="AK193" s="2"/>
+      <c r="AI193" s="8"/>
+      <c r="AJ193" s="8"/>
+      <c r="AK193" s="8"/>
       <c r="AL193" s="2"/>
       <c r="AM193" s="2"/>
       <c r="AN193" s="2"/>
@@ -17769,8 +18417,11 @@
       <c r="CD193" s="2"/>
       <c r="CE193" s="2"/>
       <c r="CF193" s="2"/>
-    </row>
-    <row r="194" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG193" s="2"/>
+      <c r="CH193" s="2"/>
+      <c r="CI193" s="2"/>
+    </row>
+    <row r="194" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -17805,9 +18456,9 @@
       <c r="AF194" s="2"/>
       <c r="AG194" s="2"/>
       <c r="AH194" s="2"/>
-      <c r="AI194" s="2"/>
-      <c r="AJ194" s="2"/>
-      <c r="AK194" s="2"/>
+      <c r="AI194" s="8"/>
+      <c r="AJ194" s="8"/>
+      <c r="AK194" s="8"/>
       <c r="AL194" s="2"/>
       <c r="AM194" s="2"/>
       <c r="AN194" s="2"/>
@@ -17855,8 +18506,11 @@
       <c r="CD194" s="2"/>
       <c r="CE194" s="2"/>
       <c r="CF194" s="2"/>
-    </row>
-    <row r="195" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG194" s="2"/>
+      <c r="CH194" s="2"/>
+      <c r="CI194" s="2"/>
+    </row>
+    <row r="195" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -17891,9 +18545,9 @@
       <c r="AF195" s="2"/>
       <c r="AG195" s="2"/>
       <c r="AH195" s="2"/>
-      <c r="AI195" s="2"/>
-      <c r="AJ195" s="2"/>
-      <c r="AK195" s="2"/>
+      <c r="AI195" s="8"/>
+      <c r="AJ195" s="8"/>
+      <c r="AK195" s="8"/>
       <c r="AL195" s="2"/>
       <c r="AM195" s="2"/>
       <c r="AN195" s="2"/>
@@ -17941,8 +18595,11 @@
       <c r="CD195" s="2"/>
       <c r="CE195" s="2"/>
       <c r="CF195" s="2"/>
-    </row>
-    <row r="196" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG195" s="2"/>
+      <c r="CH195" s="2"/>
+      <c r="CI195" s="2"/>
+    </row>
+    <row r="196" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -17977,9 +18634,9 @@
       <c r="AF196" s="2"/>
       <c r="AG196" s="2"/>
       <c r="AH196" s="2"/>
-      <c r="AI196" s="2"/>
-      <c r="AJ196" s="2"/>
-      <c r="AK196" s="2"/>
+      <c r="AI196" s="8"/>
+      <c r="AJ196" s="8"/>
+      <c r="AK196" s="8"/>
       <c r="AL196" s="2"/>
       <c r="AM196" s="2"/>
       <c r="AN196" s="2"/>
@@ -18027,8 +18684,11 @@
       <c r="CD196" s="2"/>
       <c r="CE196" s="2"/>
       <c r="CF196" s="2"/>
-    </row>
-    <row r="197" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG196" s="2"/>
+      <c r="CH196" s="2"/>
+      <c r="CI196" s="2"/>
+    </row>
+    <row r="197" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -18063,9 +18723,9 @@
       <c r="AF197" s="2"/>
       <c r="AG197" s="2"/>
       <c r="AH197" s="2"/>
-      <c r="AI197" s="2"/>
-      <c r="AJ197" s="2"/>
-      <c r="AK197" s="2"/>
+      <c r="AI197" s="8"/>
+      <c r="AJ197" s="8"/>
+      <c r="AK197" s="8"/>
       <c r="AL197" s="2"/>
       <c r="AM197" s="2"/>
       <c r="AN197" s="2"/>
@@ -18113,8 +18773,11 @@
       <c r="CD197" s="2"/>
       <c r="CE197" s="2"/>
       <c r="CF197" s="2"/>
-    </row>
-    <row r="198" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG197" s="2"/>
+      <c r="CH197" s="2"/>
+      <c r="CI197" s="2"/>
+    </row>
+    <row r="198" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -18149,9 +18812,9 @@
       <c r="AF198" s="2"/>
       <c r="AG198" s="2"/>
       <c r="AH198" s="2"/>
-      <c r="AI198" s="2"/>
-      <c r="AJ198" s="2"/>
-      <c r="AK198" s="2"/>
+      <c r="AI198" s="8"/>
+      <c r="AJ198" s="8"/>
+      <c r="AK198" s="8"/>
       <c r="AL198" s="2"/>
       <c r="AM198" s="2"/>
       <c r="AN198" s="2"/>
@@ -18199,8 +18862,11 @@
       <c r="CD198" s="2"/>
       <c r="CE198" s="2"/>
       <c r="CF198" s="2"/>
-    </row>
-    <row r="199" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG198" s="2"/>
+      <c r="CH198" s="2"/>
+      <c r="CI198" s="2"/>
+    </row>
+    <row r="199" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -18235,9 +18901,9 @@
       <c r="AF199" s="2"/>
       <c r="AG199" s="2"/>
       <c r="AH199" s="2"/>
-      <c r="AI199" s="2"/>
-      <c r="AJ199" s="2"/>
-      <c r="AK199" s="2"/>
+      <c r="AI199" s="8"/>
+      <c r="AJ199" s="8"/>
+      <c r="AK199" s="8"/>
       <c r="AL199" s="2"/>
       <c r="AM199" s="2"/>
       <c r="AN199" s="2"/>
@@ -18285,8 +18951,11 @@
       <c r="CD199" s="2"/>
       <c r="CE199" s="2"/>
       <c r="CF199" s="2"/>
-    </row>
-    <row r="200" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG199" s="2"/>
+      <c r="CH199" s="2"/>
+      <c r="CI199" s="2"/>
+    </row>
+    <row r="200" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -18321,9 +18990,9 @@
       <c r="AF200" s="2"/>
       <c r="AG200" s="2"/>
       <c r="AH200" s="2"/>
-      <c r="AI200" s="2"/>
-      <c r="AJ200" s="2"/>
-      <c r="AK200" s="2"/>
+      <c r="AI200" s="8"/>
+      <c r="AJ200" s="8"/>
+      <c r="AK200" s="8"/>
       <c r="AL200" s="2"/>
       <c r="AM200" s="2"/>
       <c r="AN200" s="2"/>
@@ -18371,8 +19040,11 @@
       <c r="CD200" s="2"/>
       <c r="CE200" s="2"/>
       <c r="CF200" s="2"/>
-    </row>
-    <row r="201" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG200" s="2"/>
+      <c r="CH200" s="2"/>
+      <c r="CI200" s="2"/>
+    </row>
+    <row r="201" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -18407,9 +19079,9 @@
       <c r="AF201" s="2"/>
       <c r="AG201" s="2"/>
       <c r="AH201" s="2"/>
-      <c r="AI201" s="2"/>
-      <c r="AJ201" s="2"/>
-      <c r="AK201" s="2"/>
+      <c r="AI201" s="8"/>
+      <c r="AJ201" s="8"/>
+      <c r="AK201" s="8"/>
       <c r="AL201" s="2"/>
       <c r="AM201" s="2"/>
       <c r="AN201" s="2"/>
@@ -18457,8 +19129,11 @@
       <c r="CD201" s="2"/>
       <c r="CE201" s="2"/>
       <c r="CF201" s="2"/>
-    </row>
-    <row r="202" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="CG201" s="2"/>
+      <c r="CH201" s="2"/>
+      <c r="CI201" s="2"/>
+    </row>
+    <row r="202" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -18493,9 +19168,9 @@
       <c r="AF202" s="2"/>
       <c r="AG202" s="2"/>
       <c r="AH202" s="2"/>
-      <c r="AI202" s="2"/>
-      <c r="AJ202" s="2"/>
-      <c r="AK202" s="2"/>
+      <c r="AI202" s="8"/>
+      <c r="AJ202" s="8"/>
+      <c r="AK202" s="8"/>
       <c r="AL202" s="2"/>
       <c r="AM202" s="2"/>
       <c r="AN202" s="2"/>
@@ -18543,17 +19218,21 @@
       <c r="CD202" s="2"/>
       <c r="CE202" s="2"/>
       <c r="CF202" s="2"/>
+      <c r="CG202" s="2"/>
+      <c r="CH202" s="2"/>
+      <c r="CI202" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="BR1:CF1"/>
-    <mergeCell ref="BE1:BQ1"/>
-    <mergeCell ref="AV1:BD1"/>
-    <mergeCell ref="AI1:AU1"/>
+  <mergeCells count="9">
+    <mergeCell ref="BU1:CI1"/>
+    <mergeCell ref="BH1:BT1"/>
+    <mergeCell ref="AI1:AK1"/>
+    <mergeCell ref="AL1:AX1"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="U1:AF1"/>
     <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="AY1:BG1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test_data/PQME_Encounter_Test_Data.xlsx
+++ b/test_data/PQME_Encounter_Test_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Rishi Files\OrthoLegal_Automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B521AA1F-2FC3-4214-9365-E7382A67FD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E84B68-21C1-4209-BEB6-E378DB1A9EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1092" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Encounter_Test_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="117">
   <si>
     <t>Applicant Details</t>
   </si>
@@ -196,15 +196,6 @@
     <t>Adjuster Assistant Email</t>
   </si>
   <si>
-    <t>ANeoers</t>
-  </si>
-  <si>
-    <t>Devtest</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -374,6 +365,12 @@
   </si>
   <si>
     <t>(714) 555-2389</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Kumar</t>
   </si>
 </sst>
 </file>
@@ -1256,73 +1253,73 @@
     </row>
     <row r="3" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="3">
+        <v>36608</v>
+      </c>
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="3">
-        <v>31758</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>61</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>62</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="H3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="K3">
         <v>94612</v>
       </c>
       <c r="L3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" t="s">
         <v>67</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
         <v>68</v>
       </c>
-      <c r="N3" t="s">
+      <c r="Q3" t="s">
         <v>69</v>
       </c>
-      <c r="O3" t="s">
+      <c r="R3" t="s">
         <v>70</v>
       </c>
-      <c r="P3" t="s">
+      <c r="S3" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="T3" t="s">
         <v>72</v>
       </c>
-      <c r="R3" t="s">
+      <c r="U3" t="s">
         <v>73</v>
       </c>
-      <c r="S3" t="s">
+      <c r="V3" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="T3" t="s">
+      <c r="W3" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="U3" t="s">
-        <v>76</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="X3" s="4">
         <v>10000000000</v>
@@ -1334,16 +1331,16 @@
         <v>46335.416666666664</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AE3" s="4">
         <v>92626</v>
@@ -1352,163 +1349,163 @@
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AJ3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AK3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AL3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO3" t="s">
         <v>82</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AP3" t="s">
         <v>83</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AQ3" t="s">
         <v>84</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AR3" t="s">
         <v>85</v>
       </c>
-      <c r="AP3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>88</v>
-      </c>
       <c r="AS3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AT3">
         <v>90001</v>
       </c>
       <c r="AU3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AX3" t="s">
         <v>89</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AY3" t="s">
         <v>90</v>
       </c>
-      <c r="AW3" t="s">
+      <c r="AZ3" t="s">
         <v>91</v>
       </c>
-      <c r="AX3" t="s">
+      <c r="BA3" t="s">
         <v>92</v>
       </c>
-      <c r="AY3" t="s">
-        <v>93</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>95</v>
-      </c>
       <c r="BB3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="BD3">
         <v>90001</v>
       </c>
       <c r="BE3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>95</v>
+      </c>
+      <c r="BH3" t="s">
         <v>96</v>
       </c>
-      <c r="BF3" t="s">
+      <c r="BI3" t="s">
         <v>97</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BJ3" t="s">
         <v>98</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BK3" t="s">
         <v>99</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BL3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BM3" t="s">
         <v>100</v>
       </c>
-      <c r="BJ3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>102</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>103</v>
-      </c>
       <c r="BN3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="BP3">
         <v>90001</v>
       </c>
       <c r="BQ3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>102</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT3" t="s">
         <v>104</v>
       </c>
-      <c r="BR3" t="s">
+      <c r="BU3" t="s">
         <v>105</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BV3" t="s">
         <v>106</v>
       </c>
-      <c r="BT3" t="s">
+      <c r="BW3" t="s">
         <v>107</v>
       </c>
-      <c r="BU3" t="s">
+      <c r="BX3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BY3" t="s">
         <v>108</v>
       </c>
-      <c r="BV3" t="s">
+      <c r="BZ3" t="s">
         <v>109</v>
       </c>
-      <c r="BW3" t="s">
-        <v>110</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>83</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>111</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>112</v>
-      </c>
       <c r="CA3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="CB3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="CC3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="CD3" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="CE3">
         <v>90001</v>
       </c>
       <c r="CF3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="CG3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="CH3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="CI3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.25">
